--- a/Odds-Data-Clean/2011-12.xlsx
+++ b/Odds-Data-Clean/2011-12.xlsx
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2011-12-101</t>
+          <t>2011-12-0101</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2011-12-101</t>
+          <t>2011-12-0101</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2011-12-101</t>
+          <t>2011-12-0101</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2011-12-101</t>
+          <t>2011-12-0101</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2011-12-101</t>
+          <t>2011-12-0101</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2011-12-101</t>
+          <t>2011-12-0101</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2011-12-101</t>
+          <t>2011-12-0101</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2011-12-101</t>
+          <t>2011-12-0101</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2011-12-101</t>
+          <t>2011-12-0101</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2011-12-102</t>
+          <t>2011-12-0102</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2011-12-102</t>
+          <t>2011-12-0102</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2011-12-102</t>
+          <t>2011-12-0102</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2011-12-102</t>
+          <t>2011-12-0102</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3312,7 +3312,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2011-12-102</t>
+          <t>2011-12-0102</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2011-12-102</t>
+          <t>2011-12-0102</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2011-12-102</t>
+          <t>2011-12-0102</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2011-12-102</t>
+          <t>2011-12-0102</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2011-12-102</t>
+          <t>2011-12-0102</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2011-12-102</t>
+          <t>2011-12-0102</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2011-12-103</t>
+          <t>2011-12-0103</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2011-12-103</t>
+          <t>2011-12-0103</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2011-12-103</t>
+          <t>2011-12-0103</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2011-12-103</t>
+          <t>2011-12-0103</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2011-12-103</t>
+          <t>2011-12-0103</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2011-12-103</t>
+          <t>2011-12-0103</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2011-12-104</t>
+          <t>2011-12-0104</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2011-12-104</t>
+          <t>2011-12-0104</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2011-12-104</t>
+          <t>2011-12-0104</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2011-12-104</t>
+          <t>2011-12-0104</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2011-12-104</t>
+          <t>2011-12-0104</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2011-12-104</t>
+          <t>2011-12-0104</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2011-12-104</t>
+          <t>2011-12-0104</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2011-12-104</t>
+          <t>2011-12-0104</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2011-12-104</t>
+          <t>2011-12-0104</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2011-12-104</t>
+          <t>2011-12-0104</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2011-12-104</t>
+          <t>2011-12-0104</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2011-12-104</t>
+          <t>2011-12-0104</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2011-12-105</t>
+          <t>2011-12-0105</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2011-12-105</t>
+          <t>2011-12-0105</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2011-12-105</t>
+          <t>2011-12-0105</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2011-12-105</t>
+          <t>2011-12-0105</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2011-12-106</t>
+          <t>2011-12-0106</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2011-12-106</t>
+          <t>2011-12-0106</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2011-12-106</t>
+          <t>2011-12-0106</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2011-12-106</t>
+          <t>2011-12-0106</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2011-12-106</t>
+          <t>2011-12-0106</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2011-12-106</t>
+          <t>2011-12-0106</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2011-12-106</t>
+          <t>2011-12-0106</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2011-12-106</t>
+          <t>2011-12-0106</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2011-12-106</t>
+          <t>2011-12-0106</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2011-12-106</t>
+          <t>2011-12-0106</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2011-12-106</t>
+          <t>2011-12-0106</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2011-12-106</t>
+          <t>2011-12-0106</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2011-12-107</t>
+          <t>2011-12-0107</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2011-12-107</t>
+          <t>2011-12-0107</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2011-12-107</t>
+          <t>2011-12-0107</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2011-12-107</t>
+          <t>2011-12-0107</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2011-12-107</t>
+          <t>2011-12-0107</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2011-12-107</t>
+          <t>2011-12-0107</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2011-12-107</t>
+          <t>2011-12-0107</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2011-12-107</t>
+          <t>2011-12-0107</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2011-12-107</t>
+          <t>2011-12-0107</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2011-12-107</t>
+          <t>2011-12-0107</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2011-12-108</t>
+          <t>2011-12-0108</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2011-12-108</t>
+          <t>2011-12-0108</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2011-12-108</t>
+          <t>2011-12-0108</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2011-12-108</t>
+          <t>2011-12-0108</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2011-12-108</t>
+          <t>2011-12-0108</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2011-12-108</t>
+          <t>2011-12-0108</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2011-12-109</t>
+          <t>2011-12-0109</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2011-12-109</t>
+          <t>2011-12-0109</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2011-12-109</t>
+          <t>2011-12-0109</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2011-12-109</t>
+          <t>2011-12-0109</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2011-12-109</t>
+          <t>2011-12-0109</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2011-12-109</t>
+          <t>2011-12-0109</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2011-12-110</t>
+          <t>2011-12-0110</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2011-12-110</t>
+          <t>2011-12-0110</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2011-12-110</t>
+          <t>2011-12-0110</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2011-12-110</t>
+          <t>2011-12-0110</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2011-12-110</t>
+          <t>2011-12-0110</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2011-12-110</t>
+          <t>2011-12-0110</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2011-12-110</t>
+          <t>2011-12-0110</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2011-12-110</t>
+          <t>2011-12-0110</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -6252,7 +6252,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2011-12-110</t>
+          <t>2011-12-0110</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2011-12-110</t>
+          <t>2011-12-0110</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2011-12-110</t>
+          <t>2011-12-0110</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2011-12-111</t>
+          <t>2011-12-0111</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2011-12-111</t>
+          <t>2011-12-0111</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2011-12-111</t>
+          <t>2011-12-0111</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2011-12-111</t>
+          <t>2011-12-0111</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2011-12-111</t>
+          <t>2011-12-0111</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2011-12-111</t>
+          <t>2011-12-0111</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2011-12-111</t>
+          <t>2011-12-0111</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2011-12-111</t>
+          <t>2011-12-0111</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2011-12-111</t>
+          <t>2011-12-0111</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2011-12-111</t>
+          <t>2011-12-0111</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2011-12-111</t>
+          <t>2011-12-0111</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2011-12-112</t>
+          <t>2011-12-0112</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2011-12-112</t>
+          <t>2011-12-0112</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2011-12-112</t>
+          <t>2011-12-0112</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2011-12-112</t>
+          <t>2011-12-0112</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2011-12-112</t>
+          <t>2011-12-0112</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2011-12-113</t>
+          <t>2011-12-0113</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2011-12-113</t>
+          <t>2011-12-0113</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2011-12-113</t>
+          <t>2011-12-0113</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2011-12-113</t>
+          <t>2011-12-0113</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2011-12-113</t>
+          <t>2011-12-0113</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2011-12-113</t>
+          <t>2011-12-0113</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2011-12-113</t>
+          <t>2011-12-0113</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2011-12-113</t>
+          <t>2011-12-0113</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2011-12-113</t>
+          <t>2011-12-0113</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2011-12-113</t>
+          <t>2011-12-0113</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2011-12-113</t>
+          <t>2011-12-0113</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2011-12-114</t>
+          <t>2011-12-0114</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2011-12-114</t>
+          <t>2011-12-0114</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2011-12-114</t>
+          <t>2011-12-0114</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2011-12-114</t>
+          <t>2011-12-0114</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2011-12-114</t>
+          <t>2011-12-0114</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2011-12-114</t>
+          <t>2011-12-0114</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2011-12-114</t>
+          <t>2011-12-0114</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2011-12-114</t>
+          <t>2011-12-0114</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2011-12-114</t>
+          <t>2011-12-0114</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2011-12-114</t>
+          <t>2011-12-0114</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2011-12-114</t>
+          <t>2011-12-0114</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2011-12-115</t>
+          <t>2011-12-0115</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2011-12-115</t>
+          <t>2011-12-0115</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -8058,7 +8058,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2011-12-115</t>
+          <t>2011-12-0115</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2011-12-116</t>
+          <t>2011-12-0116</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2011-12-116</t>
+          <t>2011-12-0116</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2011-12-116</t>
+          <t>2011-12-0116</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2011-12-116</t>
+          <t>2011-12-0116</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2011-12-116</t>
+          <t>2011-12-0116</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2011-12-116</t>
+          <t>2011-12-0116</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2011-12-116</t>
+          <t>2011-12-0116</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2011-12-116</t>
+          <t>2011-12-0116</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2011-12-116</t>
+          <t>2011-12-0116</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2011-12-116</t>
+          <t>2011-12-0116</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2011-12-116</t>
+          <t>2011-12-0116</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2011-12-117</t>
+          <t>2011-12-0117</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2011-12-117</t>
+          <t>2011-12-0117</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2011-12-117</t>
+          <t>2011-12-0117</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2011-12-117</t>
+          <t>2011-12-0117</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -8730,7 +8730,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2011-12-117</t>
+          <t>2011-12-0117</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2011-12-117</t>
+          <t>2011-12-0117</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2011-12-117</t>
+          <t>2011-12-0117</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2011-12-118</t>
+          <t>2011-12-0118</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2011-12-118</t>
+          <t>2011-12-0118</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2011-12-118</t>
+          <t>2011-12-0118</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -8982,7 +8982,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2011-12-118</t>
+          <t>2011-12-0118</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -9024,7 +9024,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2011-12-118</t>
+          <t>2011-12-0118</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2011-12-118</t>
+          <t>2011-12-0118</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2011-12-118</t>
+          <t>2011-12-0118</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2011-12-118</t>
+          <t>2011-12-0118</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2011-12-118</t>
+          <t>2011-12-0118</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2011-12-118</t>
+          <t>2011-12-0118</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2011-12-118</t>
+          <t>2011-12-0118</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2011-12-119</t>
+          <t>2011-12-0119</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2011-12-119</t>
+          <t>2011-12-0119</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2011-12-119</t>
+          <t>2011-12-0119</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -9444,7 +9444,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2011-12-120</t>
+          <t>2011-12-0120</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2011-12-120</t>
+          <t>2011-12-0120</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2011-12-120</t>
+          <t>2011-12-0120</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2011-12-120</t>
+          <t>2011-12-0120</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2011-12-120</t>
+          <t>2011-12-0120</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2011-12-120</t>
+          <t>2011-12-0120</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2011-12-120</t>
+          <t>2011-12-0120</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2011-12-120</t>
+          <t>2011-12-0120</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2011-12-120</t>
+          <t>2011-12-0120</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2011-12-120</t>
+          <t>2011-12-0120</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -9864,7 +9864,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2011-12-120</t>
+          <t>2011-12-0120</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2011-12-121</t>
+          <t>2011-12-0121</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2011-12-121</t>
+          <t>2011-12-0121</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -9990,7 +9990,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2011-12-121</t>
+          <t>2011-12-0121</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2011-12-121</t>
+          <t>2011-12-0121</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2011-12-121</t>
+          <t>2011-12-0121</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2011-12-121</t>
+          <t>2011-12-0121</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2011-12-121</t>
+          <t>2011-12-0121</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -10200,7 +10200,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2011-12-121</t>
+          <t>2011-12-0121</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2011-12-121</t>
+          <t>2011-12-0121</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -10284,7 +10284,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2011-12-121</t>
+          <t>2011-12-0121</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2011-12-122</t>
+          <t>2011-12-0122</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2011-12-122</t>
+          <t>2011-12-0122</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -10410,7 +10410,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2011-12-122</t>
+          <t>2011-12-0122</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -10452,7 +10452,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2011-12-122</t>
+          <t>2011-12-0122</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -10494,7 +10494,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2011-12-122</t>
+          <t>2011-12-0122</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2011-12-123</t>
+          <t>2011-12-0123</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2011-12-123</t>
+          <t>2011-12-0123</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2011-12-123</t>
+          <t>2011-12-0123</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2011-12-123</t>
+          <t>2011-12-0123</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -10704,7 +10704,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2011-12-123</t>
+          <t>2011-12-0123</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2011-12-123</t>
+          <t>2011-12-0123</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2011-12-123</t>
+          <t>2011-12-0123</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2011-12-123</t>
+          <t>2011-12-0123</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2011-12-123</t>
+          <t>2011-12-0123</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2011-12-123</t>
+          <t>2011-12-0123</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2011-12-124</t>
+          <t>2011-12-0124</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -10998,7 +10998,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2011-12-124</t>
+          <t>2011-12-0124</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -11040,7 +11040,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2011-12-124</t>
+          <t>2011-12-0124</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2011-12-124</t>
+          <t>2011-12-0124</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -11124,7 +11124,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2011-12-124</t>
+          <t>2011-12-0124</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2011-12-125</t>
+          <t>2011-12-0125</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -11208,7 +11208,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2011-12-125</t>
+          <t>2011-12-0125</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -11250,7 +11250,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2011-12-125</t>
+          <t>2011-12-0125</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2011-12-125</t>
+          <t>2011-12-0125</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -11334,7 +11334,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2011-12-125</t>
+          <t>2011-12-0125</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -11376,7 +11376,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2011-12-125</t>
+          <t>2011-12-0125</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -11418,7 +11418,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2011-12-125</t>
+          <t>2011-12-0125</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -11460,7 +11460,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2011-12-125</t>
+          <t>2011-12-0125</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2011-12-125</t>
+          <t>2011-12-0125</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -11544,7 +11544,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2011-12-125</t>
+          <t>2011-12-0125</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2011-12-125</t>
+          <t>2011-12-0125</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -11628,7 +11628,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2011-12-125</t>
+          <t>2011-12-0125</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2011-12-125</t>
+          <t>2011-12-0125</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2011-12-126</t>
+          <t>2011-12-0126</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -11754,7 +11754,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2011-12-126</t>
+          <t>2011-12-0126</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -11796,7 +11796,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2011-12-127</t>
+          <t>2011-12-0127</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2011-12-127</t>
+          <t>2011-12-0127</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2011-12-127</t>
+          <t>2011-12-0127</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2011-12-127</t>
+          <t>2011-12-0127</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2011-12-127</t>
+          <t>2011-12-0127</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -12006,7 +12006,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2011-12-127</t>
+          <t>2011-12-0127</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -12048,7 +12048,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2011-12-127</t>
+          <t>2011-12-0127</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2011-12-127</t>
+          <t>2011-12-0127</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2011-12-127</t>
+          <t>2011-12-0127</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2011-12-127</t>
+          <t>2011-12-0127</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -12216,7 +12216,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2011-12-127</t>
+          <t>2011-12-0127</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2011-12-127</t>
+          <t>2011-12-0127</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -12300,7 +12300,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2011-12-127</t>
+          <t>2011-12-0127</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -12342,7 +12342,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2011-12-128</t>
+          <t>2011-12-0128</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -12384,7 +12384,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2011-12-128</t>
+          <t>2011-12-0128</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2011-12-128</t>
+          <t>2011-12-0128</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2011-12-128</t>
+          <t>2011-12-0128</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2011-12-128</t>
+          <t>2011-12-0128</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -12552,7 +12552,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2011-12-128</t>
+          <t>2011-12-0128</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -12594,7 +12594,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2011-12-129</t>
+          <t>2011-12-0129</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -12636,7 +12636,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2011-12-129</t>
+          <t>2011-12-0129</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2011-12-129</t>
+          <t>2011-12-0129</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -12720,7 +12720,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2011-12-129</t>
+          <t>2011-12-0129</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -12762,7 +12762,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2011-12-129</t>
+          <t>2011-12-0129</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -12804,7 +12804,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2011-12-129</t>
+          <t>2011-12-0129</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2011-12-129</t>
+          <t>2011-12-0129</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2011-12-129</t>
+          <t>2011-12-0129</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -12930,7 +12930,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2011-12-130</t>
+          <t>2011-12-0130</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2011-12-130</t>
+          <t>2011-12-0130</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -13014,7 +13014,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2011-12-130</t>
+          <t>2011-12-0130</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -13056,7 +13056,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2011-12-130</t>
+          <t>2011-12-0130</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2011-12-130</t>
+          <t>2011-12-0130</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -13140,7 +13140,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2011-12-130</t>
+          <t>2011-12-0130</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -13182,7 +13182,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2011-12-130</t>
+          <t>2011-12-0130</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2011-12-130</t>
+          <t>2011-12-0130</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2011-12-130</t>
+          <t>2011-12-0130</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2011-12-131</t>
+          <t>2011-12-0131</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -13350,7 +13350,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2011-12-131</t>
+          <t>2011-12-0131</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -13392,7 +13392,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2011-12-131</t>
+          <t>2011-12-0131</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2011-12-131</t>
+          <t>2011-12-0131</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2011-12-131</t>
+          <t>2011-12-0131</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -13518,7 +13518,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2011-12-131</t>
+          <t>2011-12-0131</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -13560,7 +13560,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2011-12-131</t>
+          <t>2011-12-0131</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2011-12-201</t>
+          <t>2011-12-0201</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2011-12-201</t>
+          <t>2011-12-0201</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -13686,7 +13686,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2011-12-201</t>
+          <t>2011-12-0201</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -13728,7 +13728,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2011-12-201</t>
+          <t>2011-12-0201</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -13770,7 +13770,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2011-12-201</t>
+          <t>2011-12-0201</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -13812,7 +13812,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2011-12-201</t>
+          <t>2011-12-0201</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -13854,7 +13854,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2011-12-201</t>
+          <t>2011-12-0201</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -13896,7 +13896,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2011-12-201</t>
+          <t>2011-12-0201</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -13938,7 +13938,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2011-12-201</t>
+          <t>2011-12-0201</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2011-12-201</t>
+          <t>2011-12-0201</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -14022,7 +14022,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2011-12-201</t>
+          <t>2011-12-0201</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -14064,7 +14064,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2011-12-202</t>
+          <t>2011-12-0202</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -14106,7 +14106,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2011-12-202</t>
+          <t>2011-12-0202</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2011-12-202</t>
+          <t>2011-12-0202</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2011-12-202</t>
+          <t>2011-12-0202</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -14232,7 +14232,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>2011-12-202</t>
+          <t>2011-12-0202</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>2011-12-202</t>
+          <t>2011-12-0202</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -14316,7 +14316,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>2011-12-203</t>
+          <t>2011-12-0203</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -14358,7 +14358,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>2011-12-203</t>
+          <t>2011-12-0203</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>2011-12-203</t>
+          <t>2011-12-0203</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -14442,7 +14442,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>2011-12-203</t>
+          <t>2011-12-0203</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -14484,7 +14484,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>2011-12-203</t>
+          <t>2011-12-0203</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -14526,7 +14526,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>2011-12-203</t>
+          <t>2011-12-0203</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -14568,7 +14568,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>2011-12-203</t>
+          <t>2011-12-0203</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>2011-12-203</t>
+          <t>2011-12-0203</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>2011-12-203</t>
+          <t>2011-12-0203</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>2011-12-203</t>
+          <t>2011-12-0203</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -14736,7 +14736,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>2011-12-204</t>
+          <t>2011-12-0204</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -14778,7 +14778,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>2011-12-204</t>
+          <t>2011-12-0204</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -14820,7 +14820,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>2011-12-204</t>
+          <t>2011-12-0204</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -14862,7 +14862,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>2011-12-204</t>
+          <t>2011-12-0204</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -14904,7 +14904,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>2011-12-204</t>
+          <t>2011-12-0204</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -14946,7 +14946,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>2011-12-204</t>
+          <t>2011-12-0204</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -14988,7 +14988,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>2011-12-204</t>
+          <t>2011-12-0204</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -15030,7 +15030,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>2011-12-204</t>
+          <t>2011-12-0204</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -15072,7 +15072,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>2011-12-204</t>
+          <t>2011-12-0204</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -15114,7 +15114,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>2011-12-204</t>
+          <t>2011-12-0204</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -15156,7 +15156,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>2011-12-204</t>
+          <t>2011-12-0204</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -15198,7 +15198,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>2011-12-204</t>
+          <t>2011-12-0204</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -15240,7 +15240,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>2011-12-204</t>
+          <t>2011-12-0204</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -15282,7 +15282,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>2011-12-205</t>
+          <t>2011-12-0205</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -15324,7 +15324,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>2011-12-205</t>
+          <t>2011-12-0205</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>2011-12-206</t>
+          <t>2011-12-0206</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -15408,7 +15408,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>2011-12-206</t>
+          <t>2011-12-0206</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -15450,7 +15450,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>2011-12-206</t>
+          <t>2011-12-0206</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -15492,7 +15492,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>2011-12-206</t>
+          <t>2011-12-0206</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -15534,7 +15534,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>2011-12-206</t>
+          <t>2011-12-0206</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -15576,7 +15576,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>2011-12-206</t>
+          <t>2011-12-0206</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -15618,7 +15618,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>2011-12-206</t>
+          <t>2011-12-0206</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -15660,7 +15660,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>2011-12-206</t>
+          <t>2011-12-0206</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -15702,7 +15702,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>2011-12-206</t>
+          <t>2011-12-0206</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -15744,7 +15744,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>2011-12-206</t>
+          <t>2011-12-0206</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -15786,7 +15786,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>2011-12-207</t>
+          <t>2011-12-0207</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -15828,7 +15828,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>2011-12-207</t>
+          <t>2011-12-0207</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -15870,7 +15870,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>2011-12-207</t>
+          <t>2011-12-0207</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -15912,7 +15912,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>2011-12-207</t>
+          <t>2011-12-0207</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -15954,7 +15954,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>2011-12-207</t>
+          <t>2011-12-0207</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -15996,7 +15996,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>2011-12-207</t>
+          <t>2011-12-0207</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -16038,7 +16038,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>2011-12-208</t>
+          <t>2011-12-0208</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -16080,7 +16080,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>2011-12-208</t>
+          <t>2011-12-0208</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -16122,7 +16122,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>2011-12-208</t>
+          <t>2011-12-0208</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -16164,7 +16164,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>2011-12-208</t>
+          <t>2011-12-0208</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -16206,7 +16206,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>2011-12-208</t>
+          <t>2011-12-0208</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -16248,7 +16248,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>2011-12-208</t>
+          <t>2011-12-0208</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -16290,7 +16290,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>2011-12-208</t>
+          <t>2011-12-0208</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -16332,7 +16332,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>2011-12-208</t>
+          <t>2011-12-0208</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -16374,7 +16374,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>2011-12-208</t>
+          <t>2011-12-0208</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -16416,7 +16416,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>2011-12-208</t>
+          <t>2011-12-0208</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -16458,7 +16458,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>2011-12-208</t>
+          <t>2011-12-0208</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>2011-12-209</t>
+          <t>2011-12-0209</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -16542,7 +16542,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>2011-12-209</t>
+          <t>2011-12-0209</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>2011-12-209</t>
+          <t>2011-12-0209</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -16626,7 +16626,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>2011-12-209</t>
+          <t>2011-12-0209</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -16668,7 +16668,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>2011-12-210</t>
+          <t>2011-12-0210</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>2011-12-210</t>
+          <t>2011-12-0210</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -16752,7 +16752,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>2011-12-210</t>
+          <t>2011-12-0210</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -16794,7 +16794,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>2011-12-210</t>
+          <t>2011-12-0210</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>2011-12-210</t>
+          <t>2011-12-0210</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -16878,7 +16878,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>2011-12-210</t>
+          <t>2011-12-0210</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -16920,7 +16920,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>2011-12-210</t>
+          <t>2011-12-0210</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -16962,7 +16962,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>2011-12-210</t>
+          <t>2011-12-0210</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -17004,7 +17004,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>2011-12-210</t>
+          <t>2011-12-0210</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -17046,7 +17046,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>2011-12-210</t>
+          <t>2011-12-0210</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -17088,7 +17088,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>2011-12-210</t>
+          <t>2011-12-0210</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -17130,7 +17130,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>2011-12-210</t>
+          <t>2011-12-0210</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -17172,7 +17172,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>2011-12-211</t>
+          <t>2011-12-0211</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -17214,7 +17214,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>2011-12-211</t>
+          <t>2011-12-0211</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -17256,7 +17256,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>2011-12-211</t>
+          <t>2011-12-0211</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -17298,7 +17298,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>2011-12-211</t>
+          <t>2011-12-0211</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -17340,7 +17340,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>2011-12-211</t>
+          <t>2011-12-0211</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>2011-12-211</t>
+          <t>2011-12-0211</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -17424,7 +17424,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>2011-12-211</t>
+          <t>2011-12-0211</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -17466,7 +17466,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>2011-12-211</t>
+          <t>2011-12-0211</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -17508,7 +17508,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>2011-12-212</t>
+          <t>2011-12-0212</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -17550,7 +17550,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>2011-12-212</t>
+          <t>2011-12-0212</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>2011-12-212</t>
+          <t>2011-12-0212</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -17634,7 +17634,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2011-12-212</t>
+          <t>2011-12-0212</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>2011-12-212</t>
+          <t>2011-12-0212</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -17718,7 +17718,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>2011-12-212</t>
+          <t>2011-12-0212</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -17760,7 +17760,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>2011-12-213</t>
+          <t>2011-12-0213</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -17802,7 +17802,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>2011-12-213</t>
+          <t>2011-12-0213</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -17844,7 +17844,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>2011-12-213</t>
+          <t>2011-12-0213</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -17886,7 +17886,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>2011-12-213</t>
+          <t>2011-12-0213</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -17928,7 +17928,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>2011-12-213</t>
+          <t>2011-12-0213</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -17970,7 +17970,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>2011-12-213</t>
+          <t>2011-12-0213</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -18012,7 +18012,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>2011-12-214</t>
+          <t>2011-12-0214</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -18054,7 +18054,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>2011-12-214</t>
+          <t>2011-12-0214</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -18096,7 +18096,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>2011-12-214</t>
+          <t>2011-12-0214</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -18138,7 +18138,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>2011-12-214</t>
+          <t>2011-12-0214</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>2011-12-214</t>
+          <t>2011-12-0214</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -18222,7 +18222,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>2011-12-214</t>
+          <t>2011-12-0214</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -18264,7 +18264,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>2011-12-214</t>
+          <t>2011-12-0214</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>2011-12-214</t>
+          <t>2011-12-0214</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -18348,7 +18348,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>2011-12-214</t>
+          <t>2011-12-0214</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -18390,7 +18390,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>2011-12-215</t>
+          <t>2011-12-0215</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -18432,7 +18432,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>2011-12-215</t>
+          <t>2011-12-0215</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -18474,7 +18474,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>2011-12-215</t>
+          <t>2011-12-0215</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -18516,7 +18516,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>2011-12-215</t>
+          <t>2011-12-0215</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -18558,7 +18558,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>2011-12-215</t>
+          <t>2011-12-0215</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -18600,7 +18600,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>2011-12-215</t>
+          <t>2011-12-0215</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -18642,7 +18642,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>2011-12-215</t>
+          <t>2011-12-0215</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -18684,7 +18684,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>2011-12-215</t>
+          <t>2011-12-0215</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -18726,7 +18726,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>2011-12-215</t>
+          <t>2011-12-0215</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -18768,7 +18768,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>2011-12-215</t>
+          <t>2011-12-0215</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -18810,7 +18810,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>2011-12-215</t>
+          <t>2011-12-0215</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -18852,7 +18852,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>2011-12-215</t>
+          <t>2011-12-0215</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -18894,7 +18894,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>2011-12-215</t>
+          <t>2011-12-0215</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -18936,7 +18936,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>2011-12-216</t>
+          <t>2011-12-0216</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -18978,7 +18978,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>2011-12-216</t>
+          <t>2011-12-0216</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -19020,7 +19020,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>2011-12-216</t>
+          <t>2011-12-0216</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -19062,7 +19062,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>2011-12-217</t>
+          <t>2011-12-0217</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -19104,7 +19104,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>2011-12-217</t>
+          <t>2011-12-0217</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -19146,7 +19146,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>2011-12-217</t>
+          <t>2011-12-0217</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -19188,7 +19188,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>2011-12-217</t>
+          <t>2011-12-0217</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -19230,7 +19230,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>2011-12-217</t>
+          <t>2011-12-0217</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -19272,7 +19272,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>2011-12-217</t>
+          <t>2011-12-0217</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -19314,7 +19314,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>2011-12-217</t>
+          <t>2011-12-0217</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -19356,7 +19356,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>2011-12-217</t>
+          <t>2011-12-0217</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -19398,7 +19398,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>2011-12-217</t>
+          <t>2011-12-0217</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -19440,7 +19440,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>2011-12-217</t>
+          <t>2011-12-0217</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>2011-12-217</t>
+          <t>2011-12-0217</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -19524,7 +19524,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>2011-12-218</t>
+          <t>2011-12-0218</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -19566,7 +19566,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>2011-12-218</t>
+          <t>2011-12-0218</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -19608,7 +19608,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>2011-12-218</t>
+          <t>2011-12-0218</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -19650,7 +19650,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>2011-12-218</t>
+          <t>2011-12-0218</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -19692,7 +19692,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>2011-12-219</t>
+          <t>2011-12-0219</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -19734,7 +19734,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>2011-12-219</t>
+          <t>2011-12-0219</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -19776,7 +19776,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>2011-12-219</t>
+          <t>2011-12-0219</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -19818,7 +19818,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>2011-12-219</t>
+          <t>2011-12-0219</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -19860,7 +19860,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>2011-12-219</t>
+          <t>2011-12-0219</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -19902,7 +19902,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>2011-12-219</t>
+          <t>2011-12-0219</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -19944,7 +19944,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>2011-12-219</t>
+          <t>2011-12-0219</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -19986,7 +19986,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>2011-12-219</t>
+          <t>2011-12-0219</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -20028,7 +20028,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>2011-12-219</t>
+          <t>2011-12-0219</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -20070,7 +20070,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>2011-12-219</t>
+          <t>2011-12-0219</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -20112,7 +20112,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>2011-12-220</t>
+          <t>2011-12-0220</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -20154,7 +20154,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>2011-12-220</t>
+          <t>2011-12-0220</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -20196,7 +20196,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>2011-12-220</t>
+          <t>2011-12-0220</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -20238,7 +20238,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>2011-12-220</t>
+          <t>2011-12-0220</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -20280,7 +20280,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>2011-12-220</t>
+          <t>2011-12-0220</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -20322,7 +20322,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>2011-12-220</t>
+          <t>2011-12-0220</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -20364,7 +20364,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>2011-12-220</t>
+          <t>2011-12-0220</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -20406,7 +20406,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>2011-12-220</t>
+          <t>2011-12-0220</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -20448,7 +20448,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>2011-12-220</t>
+          <t>2011-12-0220</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -20490,7 +20490,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>2011-12-220</t>
+          <t>2011-12-0220</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -20532,7 +20532,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>2011-12-220</t>
+          <t>2011-12-0220</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -20574,7 +20574,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>2011-12-221</t>
+          <t>2011-12-0221</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -20616,7 +20616,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>2011-12-221</t>
+          <t>2011-12-0221</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -20658,7 +20658,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>2011-12-221</t>
+          <t>2011-12-0221</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -20700,7 +20700,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>2011-12-221</t>
+          <t>2011-12-0221</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -20742,7 +20742,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>2011-12-221</t>
+          <t>2011-12-0221</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -20784,7 +20784,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>2011-12-222</t>
+          <t>2011-12-0222</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -20826,7 +20826,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>2011-12-222</t>
+          <t>2011-12-0222</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -20868,7 +20868,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>2011-12-222</t>
+          <t>2011-12-0222</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -20910,7 +20910,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>2011-12-222</t>
+          <t>2011-12-0222</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -20952,7 +20952,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>2011-12-222</t>
+          <t>2011-12-0222</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -20994,7 +20994,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>2011-12-222</t>
+          <t>2011-12-0222</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -21036,7 +21036,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>2011-12-222</t>
+          <t>2011-12-0222</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -21078,7 +21078,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>2011-12-222</t>
+          <t>2011-12-0222</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -21120,7 +21120,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>2011-12-222</t>
+          <t>2011-12-0222</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -21162,7 +21162,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>2011-12-222</t>
+          <t>2011-12-0222</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -21204,7 +21204,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>2011-12-222</t>
+          <t>2011-12-0222</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -21246,7 +21246,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>2011-12-222</t>
+          <t>2011-12-0222</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -21288,7 +21288,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>2011-12-222</t>
+          <t>2011-12-0222</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -21330,7 +21330,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>2011-12-223</t>
+          <t>2011-12-0223</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -21372,7 +21372,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>2011-12-223</t>
+          <t>2011-12-0223</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -21414,7 +21414,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>2011-12-223</t>
+          <t>2011-12-0223</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -21456,7 +21456,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>2011-12-223</t>
+          <t>2011-12-0223</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -21498,7 +21498,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>2011-12-228</t>
+          <t>2011-12-0228</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -21540,7 +21540,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>2011-12-228</t>
+          <t>2011-12-0228</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -21582,7 +21582,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>2011-12-228</t>
+          <t>2011-12-0228</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -21624,7 +21624,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>2011-12-228</t>
+          <t>2011-12-0228</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -21666,7 +21666,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>2011-12-228</t>
+          <t>2011-12-0228</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -21708,7 +21708,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>2011-12-228</t>
+          <t>2011-12-0228</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -21750,7 +21750,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>2011-12-228</t>
+          <t>2011-12-0228</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -21792,7 +21792,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>2011-12-228</t>
+          <t>2011-12-0228</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -21834,7 +21834,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>2011-12-228</t>
+          <t>2011-12-0228</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>2011-12-229</t>
+          <t>2011-12-0229</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -21918,7 +21918,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>2011-12-229</t>
+          <t>2011-12-0229</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -21960,7 +21960,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>2011-12-229</t>
+          <t>2011-12-0229</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -22002,7 +22002,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>2011-12-229</t>
+          <t>2011-12-0229</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -22044,7 +22044,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>2011-12-229</t>
+          <t>2011-12-0229</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>2011-12-229</t>
+          <t>2011-12-0229</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -22128,7 +22128,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>2011-12-229</t>
+          <t>2011-12-0229</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -22170,7 +22170,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>2011-12-229</t>
+          <t>2011-12-0229</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -22212,7 +22212,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>2011-12-229</t>
+          <t>2011-12-0229</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -22254,7 +22254,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>2011-12-229</t>
+          <t>2011-12-0229</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -22296,7 +22296,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>2011-12-229</t>
+          <t>2011-12-0229</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -22338,7 +22338,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>2011-12-229</t>
+          <t>2011-12-0229</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -22380,7 +22380,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>2011-12-301</t>
+          <t>2011-12-0301</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -22422,7 +22422,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>2011-12-301</t>
+          <t>2011-12-0301</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -22464,7 +22464,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>2011-12-301</t>
+          <t>2011-12-0301</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -22506,7 +22506,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>2011-12-301</t>
+          <t>2011-12-0301</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -22548,7 +22548,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>2011-12-302</t>
+          <t>2011-12-0302</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -22590,7 +22590,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>2011-12-302</t>
+          <t>2011-12-0302</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -22632,7 +22632,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>2011-12-302</t>
+          <t>2011-12-0302</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -22674,7 +22674,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>2011-12-302</t>
+          <t>2011-12-0302</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -22716,7 +22716,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>2011-12-302</t>
+          <t>2011-12-0302</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -22758,7 +22758,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>2011-12-302</t>
+          <t>2011-12-0302</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -22800,7 +22800,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>2011-12-302</t>
+          <t>2011-12-0302</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -22842,7 +22842,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>2011-12-302</t>
+          <t>2011-12-0302</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -22884,7 +22884,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>2011-12-302</t>
+          <t>2011-12-0302</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -22926,7 +22926,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>2011-12-302</t>
+          <t>2011-12-0302</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -22968,7 +22968,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>2011-12-302</t>
+          <t>2011-12-0302</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -23010,7 +23010,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>2011-12-303</t>
+          <t>2011-12-0303</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -23052,7 +23052,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>2011-12-303</t>
+          <t>2011-12-0303</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -23094,7 +23094,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>2011-12-303</t>
+          <t>2011-12-0303</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -23136,7 +23136,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>2011-12-303</t>
+          <t>2011-12-0303</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -23178,7 +23178,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>2011-12-303</t>
+          <t>2011-12-0303</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -23220,7 +23220,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>2011-12-303</t>
+          <t>2011-12-0303</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -23262,7 +23262,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>2011-12-303</t>
+          <t>2011-12-0303</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -23304,7 +23304,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>2011-12-304</t>
+          <t>2011-12-0304</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -23346,7 +23346,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>2011-12-304</t>
+          <t>2011-12-0304</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -23388,7 +23388,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>2011-12-304</t>
+          <t>2011-12-0304</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -23430,7 +23430,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>2011-12-304</t>
+          <t>2011-12-0304</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -23472,7 +23472,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>2011-12-304</t>
+          <t>2011-12-0304</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -23514,7 +23514,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>2011-12-304</t>
+          <t>2011-12-0304</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -23556,7 +23556,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>2011-12-304</t>
+          <t>2011-12-0304</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -23598,7 +23598,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>2011-12-304</t>
+          <t>2011-12-0304</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -23640,7 +23640,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>2011-12-305</t>
+          <t>2011-12-0305</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -23682,7 +23682,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>2011-12-305</t>
+          <t>2011-12-0305</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>2011-12-305</t>
+          <t>2011-12-0305</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -23766,7 +23766,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>2011-12-305</t>
+          <t>2011-12-0305</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -23808,7 +23808,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>2011-12-305</t>
+          <t>2011-12-0305</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -23850,7 +23850,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>2011-12-305</t>
+          <t>2011-12-0305</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -23892,7 +23892,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>2011-12-305</t>
+          <t>2011-12-0305</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -23934,7 +23934,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>2011-12-305</t>
+          <t>2011-12-0305</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -23976,7 +23976,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>2011-12-305</t>
+          <t>2011-12-0305</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -24018,7 +24018,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>2011-12-306</t>
+          <t>2011-12-0306</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -24060,7 +24060,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>2011-12-306</t>
+          <t>2011-12-0306</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -24102,7 +24102,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>2011-12-306</t>
+          <t>2011-12-0306</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -24144,7 +24144,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>2011-12-306</t>
+          <t>2011-12-0306</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -24186,7 +24186,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>2011-12-306</t>
+          <t>2011-12-0306</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -24228,7 +24228,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>2011-12-306</t>
+          <t>2011-12-0306</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -24270,7 +24270,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>2011-12-307</t>
+          <t>2011-12-0307</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -24312,7 +24312,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>2011-12-307</t>
+          <t>2011-12-0307</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -24354,7 +24354,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>2011-12-307</t>
+          <t>2011-12-0307</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -24396,7 +24396,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>2011-12-307</t>
+          <t>2011-12-0307</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -24438,7 +24438,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>2011-12-307</t>
+          <t>2011-12-0307</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -24480,7 +24480,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>2011-12-307</t>
+          <t>2011-12-0307</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -24522,7 +24522,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>2011-12-307</t>
+          <t>2011-12-0307</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -24564,7 +24564,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>2011-12-307</t>
+          <t>2011-12-0307</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -24606,7 +24606,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>2011-12-307</t>
+          <t>2011-12-0307</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -24648,7 +24648,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>2011-12-307</t>
+          <t>2011-12-0307</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -24690,7 +24690,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>2011-12-307</t>
+          <t>2011-12-0307</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -24732,7 +24732,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>2011-12-307</t>
+          <t>2011-12-0307</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -24774,7 +24774,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>2011-12-307</t>
+          <t>2011-12-0307</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -24816,7 +24816,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>2011-12-308</t>
+          <t>2011-12-0308</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -24858,7 +24858,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>2011-12-308</t>
+          <t>2011-12-0308</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -24900,7 +24900,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>2011-12-309</t>
+          <t>2011-12-0309</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -24942,7 +24942,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>2011-12-309</t>
+          <t>2011-12-0309</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>2011-12-309</t>
+          <t>2011-12-0309</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -25026,7 +25026,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>2011-12-309</t>
+          <t>2011-12-0309</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -25068,7 +25068,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>2011-12-309</t>
+          <t>2011-12-0309</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -25110,7 +25110,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>2011-12-309</t>
+          <t>2011-12-0309</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -25152,7 +25152,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>2011-12-309</t>
+          <t>2011-12-0309</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -25194,7 +25194,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>2011-12-309</t>
+          <t>2011-12-0309</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -25236,7 +25236,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>2011-12-309</t>
+          <t>2011-12-0309</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -25278,7 +25278,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>2011-12-309</t>
+          <t>2011-12-0309</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -25320,7 +25320,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>2011-12-310</t>
+          <t>2011-12-0310</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -25362,7 +25362,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>2011-12-310</t>
+          <t>2011-12-0310</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -25404,7 +25404,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>2011-12-310</t>
+          <t>2011-12-0310</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -25446,7 +25446,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>2011-12-310</t>
+          <t>2011-12-0310</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -25488,7 +25488,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>2011-12-310</t>
+          <t>2011-12-0310</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -25530,7 +25530,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>2011-12-310</t>
+          <t>2011-12-0310</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -25572,7 +25572,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>2011-12-310</t>
+          <t>2011-12-0310</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -25614,7 +25614,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>2011-12-310</t>
+          <t>2011-12-0310</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -25656,7 +25656,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>2011-12-310</t>
+          <t>2011-12-0310</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -25698,7 +25698,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>2011-12-311</t>
+          <t>2011-12-0311</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -25740,7 +25740,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>2011-12-311</t>
+          <t>2011-12-0311</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -25782,7 +25782,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>2011-12-311</t>
+          <t>2011-12-0311</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -25824,7 +25824,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>2011-12-311</t>
+          <t>2011-12-0311</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -25866,7 +25866,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>2011-12-311</t>
+          <t>2011-12-0311</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -25908,7 +25908,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>2011-12-311</t>
+          <t>2011-12-0311</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -25950,7 +25950,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>2011-12-311</t>
+          <t>2011-12-0311</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -25992,7 +25992,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>2011-12-311</t>
+          <t>2011-12-0311</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -26034,7 +26034,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>2011-12-312</t>
+          <t>2011-12-0312</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -26076,7 +26076,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>2011-12-312</t>
+          <t>2011-12-0312</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -26118,7 +26118,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>2011-12-312</t>
+          <t>2011-12-0312</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -26160,7 +26160,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>2011-12-312</t>
+          <t>2011-12-0312</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -26202,7 +26202,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>2011-12-312</t>
+          <t>2011-12-0312</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -26244,7 +26244,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>2011-12-312</t>
+          <t>2011-12-0312</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -26286,7 +26286,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>2011-12-312</t>
+          <t>2011-12-0312</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -26328,7 +26328,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>2011-12-313</t>
+          <t>2011-12-0313</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -26370,7 +26370,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>2011-12-313</t>
+          <t>2011-12-0313</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -26412,7 +26412,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>2011-12-313</t>
+          <t>2011-12-0313</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -26454,7 +26454,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>2011-12-313</t>
+          <t>2011-12-0313</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -26496,7 +26496,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>2011-12-313</t>
+          <t>2011-12-0313</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -26538,7 +26538,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>2011-12-313</t>
+          <t>2011-12-0313</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -26580,7 +26580,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>2011-12-313</t>
+          <t>2011-12-0313</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -26622,7 +26622,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>2011-12-313</t>
+          <t>2011-12-0313</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -26664,7 +26664,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>2011-12-314</t>
+          <t>2011-12-0314</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -26706,7 +26706,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>2011-12-314</t>
+          <t>2011-12-0314</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -26748,7 +26748,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>2011-12-314</t>
+          <t>2011-12-0314</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -26790,7 +26790,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>2011-12-314</t>
+          <t>2011-12-0314</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -26832,7 +26832,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>2011-12-314</t>
+          <t>2011-12-0314</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -26874,7 +26874,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>2011-12-314</t>
+          <t>2011-12-0314</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -26916,7 +26916,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>2011-12-314</t>
+          <t>2011-12-0314</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -26958,7 +26958,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>2011-12-314</t>
+          <t>2011-12-0314</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -27000,7 +27000,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>2011-12-314</t>
+          <t>2011-12-0314</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -27042,7 +27042,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>2011-12-314</t>
+          <t>2011-12-0314</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -27084,7 +27084,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>2011-12-314</t>
+          <t>2011-12-0314</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -27126,7 +27126,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>2011-12-314</t>
+          <t>2011-12-0314</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -27168,7 +27168,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>2011-12-315</t>
+          <t>2011-12-0315</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -27210,7 +27210,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>2011-12-315</t>
+          <t>2011-12-0315</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -27252,7 +27252,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>2011-12-315</t>
+          <t>2011-12-0315</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -27294,7 +27294,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>2011-12-315</t>
+          <t>2011-12-0315</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -27336,7 +27336,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>2011-12-315</t>
+          <t>2011-12-0315</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -27378,7 +27378,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>2011-12-316</t>
+          <t>2011-12-0316</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -27420,7 +27420,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>2011-12-316</t>
+          <t>2011-12-0316</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -27462,7 +27462,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>2011-12-316</t>
+          <t>2011-12-0316</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -27504,7 +27504,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>2011-12-316</t>
+          <t>2011-12-0316</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -27546,7 +27546,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>2011-12-316</t>
+          <t>2011-12-0316</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -27588,7 +27588,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>2011-12-316</t>
+          <t>2011-12-0316</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -27630,7 +27630,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>2011-12-316</t>
+          <t>2011-12-0316</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -27672,7 +27672,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>2011-12-316</t>
+          <t>2011-12-0316</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -27714,7 +27714,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>2011-12-316</t>
+          <t>2011-12-0316</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -27756,7 +27756,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>2011-12-316</t>
+          <t>2011-12-0316</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -27798,7 +27798,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>2011-12-316</t>
+          <t>2011-12-0316</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -27840,7 +27840,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>2011-12-317</t>
+          <t>2011-12-0317</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -27882,7 +27882,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>2011-12-317</t>
+          <t>2011-12-0317</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -27924,7 +27924,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>2011-12-317</t>
+          <t>2011-12-0317</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -27966,7 +27966,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>2011-12-317</t>
+          <t>2011-12-0317</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -28008,7 +28008,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>2011-12-317</t>
+          <t>2011-12-0317</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -28050,7 +28050,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>2011-12-317</t>
+          <t>2011-12-0317</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -28092,7 +28092,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>2011-12-317</t>
+          <t>2011-12-0317</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -28134,7 +28134,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>2011-12-317</t>
+          <t>2011-12-0317</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -28176,7 +28176,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>2011-12-318</t>
+          <t>2011-12-0318</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -28218,7 +28218,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>2011-12-318</t>
+          <t>2011-12-0318</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -28260,7 +28260,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>2011-12-318</t>
+          <t>2011-12-0318</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -28302,7 +28302,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>2011-12-318</t>
+          <t>2011-12-0318</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -28344,7 +28344,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>2011-12-318</t>
+          <t>2011-12-0318</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -28386,7 +28386,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>2011-12-318</t>
+          <t>2011-12-0318</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -28428,7 +28428,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>2011-12-318</t>
+          <t>2011-12-0318</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -28470,7 +28470,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>2011-12-318</t>
+          <t>2011-12-0318</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -28512,7 +28512,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>2011-12-319</t>
+          <t>2011-12-0319</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -28554,7 +28554,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>2011-12-319</t>
+          <t>2011-12-0319</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -28596,7 +28596,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>2011-12-319</t>
+          <t>2011-12-0319</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -28638,7 +28638,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>2011-12-319</t>
+          <t>2011-12-0319</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -28680,7 +28680,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>2011-12-319</t>
+          <t>2011-12-0319</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -28722,7 +28722,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>2011-12-319</t>
+          <t>2011-12-0319</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -28764,7 +28764,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>2011-12-320</t>
+          <t>2011-12-0320</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -28806,7 +28806,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>2011-12-320</t>
+          <t>2011-12-0320</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -28848,7 +28848,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>2011-12-320</t>
+          <t>2011-12-0320</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -28890,7 +28890,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>2011-12-320</t>
+          <t>2011-12-0320</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -28932,7 +28932,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>2011-12-320</t>
+          <t>2011-12-0320</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -28974,7 +28974,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>2011-12-320</t>
+          <t>2011-12-0320</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -29016,7 +29016,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>2011-12-320</t>
+          <t>2011-12-0320</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -29058,7 +29058,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>2011-12-321</t>
+          <t>2011-12-0321</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -29100,7 +29100,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>2011-12-321</t>
+          <t>2011-12-0321</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -29142,7 +29142,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>2011-12-321</t>
+          <t>2011-12-0321</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -29184,7 +29184,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>2011-12-321</t>
+          <t>2011-12-0321</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -29226,7 +29226,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>2011-12-321</t>
+          <t>2011-12-0321</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -29268,7 +29268,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>2011-12-321</t>
+          <t>2011-12-0321</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -29310,7 +29310,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>2011-12-321</t>
+          <t>2011-12-0321</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -29352,7 +29352,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>2011-12-321</t>
+          <t>2011-12-0321</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -29394,7 +29394,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>2011-12-321</t>
+          <t>2011-12-0321</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -29436,7 +29436,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>2011-12-321</t>
+          <t>2011-12-0321</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -29478,7 +29478,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>2011-12-322</t>
+          <t>2011-12-0322</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -29520,7 +29520,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>2011-12-322</t>
+          <t>2011-12-0322</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -29562,7 +29562,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>2011-12-322</t>
+          <t>2011-12-0322</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -29604,7 +29604,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>2011-12-322</t>
+          <t>2011-12-0322</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -29646,7 +29646,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>2011-12-322</t>
+          <t>2011-12-0322</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -29688,7 +29688,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>2011-12-322</t>
+          <t>2011-12-0322</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -29730,7 +29730,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>2011-12-323</t>
+          <t>2011-12-0323</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -29772,7 +29772,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>2011-12-323</t>
+          <t>2011-12-0323</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -29814,7 +29814,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>2011-12-323</t>
+          <t>2011-12-0323</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -29856,7 +29856,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>2011-12-323</t>
+          <t>2011-12-0323</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -29898,7 +29898,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>2011-12-323</t>
+          <t>2011-12-0323</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -29940,7 +29940,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>2011-12-323</t>
+          <t>2011-12-0323</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -29982,7 +29982,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>2011-12-323</t>
+          <t>2011-12-0323</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -30024,7 +30024,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>2011-12-323</t>
+          <t>2011-12-0323</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -30066,7 +30066,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>2011-12-323</t>
+          <t>2011-12-0323</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -30108,7 +30108,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>2011-12-323</t>
+          <t>2011-12-0323</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -30150,7 +30150,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>2011-12-323</t>
+          <t>2011-12-0323</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -30192,7 +30192,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>2011-12-324</t>
+          <t>2011-12-0324</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -30234,7 +30234,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>2011-12-324</t>
+          <t>2011-12-0324</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -30276,7 +30276,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>2011-12-324</t>
+          <t>2011-12-0324</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -30318,7 +30318,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>2011-12-324</t>
+          <t>2011-12-0324</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -30360,7 +30360,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>2011-12-324</t>
+          <t>2011-12-0324</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -30402,7 +30402,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>2011-12-324</t>
+          <t>2011-12-0324</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -30444,7 +30444,7 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>2011-12-324</t>
+          <t>2011-12-0324</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -30486,7 +30486,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>2011-12-324</t>
+          <t>2011-12-0324</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -30528,7 +30528,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>2011-12-324</t>
+          <t>2011-12-0324</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -30570,7 +30570,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>2011-12-325</t>
+          <t>2011-12-0325</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -30612,7 +30612,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>2011-12-325</t>
+          <t>2011-12-0325</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -30654,7 +30654,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>2011-12-325</t>
+          <t>2011-12-0325</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -30696,7 +30696,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>2011-12-325</t>
+          <t>2011-12-0325</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -30738,7 +30738,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>2011-12-325</t>
+          <t>2011-12-0325</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -30780,7 +30780,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>2011-12-325</t>
+          <t>2011-12-0325</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -30822,7 +30822,7 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>2011-12-325</t>
+          <t>2011-12-0325</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -30864,7 +30864,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>2011-12-325</t>
+          <t>2011-12-0325</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -30906,7 +30906,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>2011-12-326</t>
+          <t>2011-12-0326</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -30948,7 +30948,7 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>2011-12-326</t>
+          <t>2011-12-0326</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -30990,7 +30990,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>2011-12-326</t>
+          <t>2011-12-0326</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -31032,7 +31032,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>2011-12-326</t>
+          <t>2011-12-0326</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -31074,7 +31074,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>2011-12-326</t>
+          <t>2011-12-0326</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -31116,7 +31116,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>2011-12-326</t>
+          <t>2011-12-0326</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -31158,7 +31158,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>2011-12-326</t>
+          <t>2011-12-0326</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -31200,7 +31200,7 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>2011-12-326</t>
+          <t>2011-12-0326</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -31242,7 +31242,7 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>2011-12-326</t>
+          <t>2011-12-0326</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -31284,7 +31284,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>2011-12-327</t>
+          <t>2011-12-0327</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -31326,7 +31326,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>2011-12-327</t>
+          <t>2011-12-0327</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -31368,7 +31368,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>2011-12-327</t>
+          <t>2011-12-0327</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -31410,7 +31410,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>2011-12-327</t>
+          <t>2011-12-0327</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -31452,7 +31452,7 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>2011-12-327</t>
+          <t>2011-12-0327</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -31494,7 +31494,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>2011-12-327</t>
+          <t>2011-12-0327</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -31536,7 +31536,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>2011-12-327</t>
+          <t>2011-12-0327</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -31578,7 +31578,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>2011-12-328</t>
+          <t>2011-12-0328</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -31620,7 +31620,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>2011-12-328</t>
+          <t>2011-12-0328</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -31662,7 +31662,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>2011-12-328</t>
+          <t>2011-12-0328</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -31704,7 +31704,7 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>2011-12-328</t>
+          <t>2011-12-0328</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -31746,7 +31746,7 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>2011-12-328</t>
+          <t>2011-12-0328</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -31788,7 +31788,7 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>2011-12-328</t>
+          <t>2011-12-0328</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -31830,7 +31830,7 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>2011-12-328</t>
+          <t>2011-12-0328</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -31872,7 +31872,7 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>2011-12-328</t>
+          <t>2011-12-0328</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -31914,7 +31914,7 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>2011-12-328</t>
+          <t>2011-12-0328</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -31956,7 +31956,7 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>2011-12-328</t>
+          <t>2011-12-0328</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -31998,7 +31998,7 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>2011-12-329</t>
+          <t>2011-12-0329</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -32040,7 +32040,7 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>2011-12-329</t>
+          <t>2011-12-0329</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -32082,7 +32082,7 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>2011-12-329</t>
+          <t>2011-12-0329</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -32124,7 +32124,7 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>2011-12-329</t>
+          <t>2011-12-0329</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -32166,7 +32166,7 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>2011-12-330</t>
+          <t>2011-12-0330</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -32208,7 +32208,7 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>2011-12-330</t>
+          <t>2011-12-0330</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -32250,7 +32250,7 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>2011-12-330</t>
+          <t>2011-12-0330</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -32292,7 +32292,7 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>2011-12-330</t>
+          <t>2011-12-0330</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -32334,7 +32334,7 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>2011-12-330</t>
+          <t>2011-12-0330</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -32376,7 +32376,7 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>2011-12-330</t>
+          <t>2011-12-0330</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -32418,7 +32418,7 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>2011-12-330</t>
+          <t>2011-12-0330</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -32460,7 +32460,7 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>2011-12-330</t>
+          <t>2011-12-0330</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -32502,7 +32502,7 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>2011-12-330</t>
+          <t>2011-12-0330</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -32544,7 +32544,7 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>2011-12-330</t>
+          <t>2011-12-0330</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -32586,7 +32586,7 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>2011-12-330</t>
+          <t>2011-12-0330</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -32628,7 +32628,7 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>2011-12-330</t>
+          <t>2011-12-0330</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -32670,7 +32670,7 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>2011-12-331</t>
+          <t>2011-12-0331</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -32712,7 +32712,7 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>2011-12-331</t>
+          <t>2011-12-0331</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -32754,7 +32754,7 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>2011-12-331</t>
+          <t>2011-12-0331</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
@@ -32796,7 +32796,7 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>2011-12-331</t>
+          <t>2011-12-0331</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -32838,7 +32838,7 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>2011-12-331</t>
+          <t>2011-12-0331</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -32880,7 +32880,7 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>2011-12-331</t>
+          <t>2011-12-0331</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -32922,7 +32922,7 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>2011-12-331</t>
+          <t>2011-12-0331</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -32964,7 +32964,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>2011-12-331</t>
+          <t>2011-12-0331</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -33006,7 +33006,7 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>2011-12-401</t>
+          <t>2011-12-0401</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -33048,7 +33048,7 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>2011-12-401</t>
+          <t>2011-12-0401</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -33090,7 +33090,7 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>2011-12-401</t>
+          <t>2011-12-0401</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
@@ -33132,7 +33132,7 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>2011-12-401</t>
+          <t>2011-12-0401</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -33174,7 +33174,7 @@
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>2011-12-401</t>
+          <t>2011-12-0401</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
@@ -33216,7 +33216,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>2011-12-401</t>
+          <t>2011-12-0401</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>2011-12-401</t>
+          <t>2011-12-0401</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
@@ -33300,7 +33300,7 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>2011-12-401</t>
+          <t>2011-12-0401</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -33342,7 +33342,7 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>2011-12-402</t>
+          <t>2011-12-0402</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -33384,7 +33384,7 @@
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>2011-12-402</t>
+          <t>2011-12-0402</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -33426,7 +33426,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>2011-12-402</t>
+          <t>2011-12-0402</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
@@ -33468,7 +33468,7 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>2011-12-402</t>
+          <t>2011-12-0402</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
@@ -33510,7 +33510,7 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>2011-12-402</t>
+          <t>2011-12-0402</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
@@ -33552,7 +33552,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>2011-12-402</t>
+          <t>2011-12-0402</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -33594,7 +33594,7 @@
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>2011-12-403</t>
+          <t>2011-12-0403</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
@@ -33636,7 +33636,7 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>2011-12-403</t>
+          <t>2011-12-0403</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
@@ -33678,7 +33678,7 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>2011-12-403</t>
+          <t>2011-12-0403</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
@@ -33720,7 +33720,7 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>2011-12-403</t>
+          <t>2011-12-0403</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -33762,7 +33762,7 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>2011-12-403</t>
+          <t>2011-12-0403</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
@@ -33804,7 +33804,7 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>2011-12-403</t>
+          <t>2011-12-0403</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
@@ -33846,7 +33846,7 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>2011-12-403</t>
+          <t>2011-12-0403</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
@@ -33888,7 +33888,7 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>2011-12-403</t>
+          <t>2011-12-0403</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -33930,7 +33930,7 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>2011-12-404</t>
+          <t>2011-12-0404</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -33972,7 +33972,7 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>2011-12-404</t>
+          <t>2011-12-0404</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -34014,7 +34014,7 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>2011-12-404</t>
+          <t>2011-12-0404</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -34056,7 +34056,7 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>2011-12-404</t>
+          <t>2011-12-0404</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -34098,7 +34098,7 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>2011-12-404</t>
+          <t>2011-12-0404</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
@@ -34140,7 +34140,7 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>2011-12-404</t>
+          <t>2011-12-0404</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
@@ -34182,7 +34182,7 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>2011-12-404</t>
+          <t>2011-12-0404</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -34224,7 +34224,7 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>2011-12-404</t>
+          <t>2011-12-0404</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -34266,7 +34266,7 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>2011-12-404</t>
+          <t>2011-12-0404</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -34308,7 +34308,7 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>2011-12-404</t>
+          <t>2011-12-0404</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
@@ -34350,7 +34350,7 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>2011-12-404</t>
+          <t>2011-12-0404</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
@@ -34392,7 +34392,7 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>2011-12-404</t>
+          <t>2011-12-0404</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
@@ -34434,7 +34434,7 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>2011-12-405</t>
+          <t>2011-12-0405</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -34476,7 +34476,7 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>2011-12-405</t>
+          <t>2011-12-0405</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
@@ -34518,7 +34518,7 @@
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>2011-12-405</t>
+          <t>2011-12-0405</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
@@ -34560,7 +34560,7 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>2011-12-405</t>
+          <t>2011-12-0405</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -34602,7 +34602,7 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>2011-12-406</t>
+          <t>2011-12-0406</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
@@ -34644,7 +34644,7 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>2011-12-406</t>
+          <t>2011-12-0406</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -34686,7 +34686,7 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>2011-12-406</t>
+          <t>2011-12-0406</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
@@ -34728,7 +34728,7 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>2011-12-406</t>
+          <t>2011-12-0406</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -34770,7 +34770,7 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>2011-12-406</t>
+          <t>2011-12-0406</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
@@ -34812,7 +34812,7 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>2011-12-406</t>
+          <t>2011-12-0406</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -34854,7 +34854,7 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>2011-12-406</t>
+          <t>2011-12-0406</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
@@ -34896,7 +34896,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>2011-12-406</t>
+          <t>2011-12-0406</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -34938,7 +34938,7 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>2011-12-406</t>
+          <t>2011-12-0406</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
@@ -34980,7 +34980,7 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>2011-12-406</t>
+          <t>2011-12-0406</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
@@ -35022,7 +35022,7 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>2011-12-406</t>
+          <t>2011-12-0406</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
@@ -35064,7 +35064,7 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>2011-12-407</t>
+          <t>2011-12-0407</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
@@ -35106,7 +35106,7 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>2011-12-407</t>
+          <t>2011-12-0407</t>
         </is>
       </c>
       <c r="C828" t="inlineStr">
@@ -35148,7 +35148,7 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>2011-12-407</t>
+          <t>2011-12-0407</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
@@ -35190,7 +35190,7 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>2011-12-407</t>
+          <t>2011-12-0407</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
@@ -35232,7 +35232,7 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>2011-12-407</t>
+          <t>2011-12-0407</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
@@ -35274,7 +35274,7 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>2011-12-407</t>
+          <t>2011-12-0407</t>
         </is>
       </c>
       <c r="C832" t="inlineStr">
@@ -35316,7 +35316,7 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>2011-12-407</t>
+          <t>2011-12-0407</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
@@ -35358,7 +35358,7 @@
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>2011-12-407</t>
+          <t>2011-12-0407</t>
         </is>
       </c>
       <c r="C834" t="inlineStr">
@@ -35400,7 +35400,7 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>2011-12-407</t>
+          <t>2011-12-0407</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
@@ -35442,7 +35442,7 @@
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>2011-12-408</t>
+          <t>2011-12-0408</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
@@ -35484,7 +35484,7 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>2011-12-408</t>
+          <t>2011-12-0408</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
@@ -35526,7 +35526,7 @@
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>2011-12-408</t>
+          <t>2011-12-0408</t>
         </is>
       </c>
       <c r="C838" t="inlineStr">
@@ -35568,7 +35568,7 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>2011-12-408</t>
+          <t>2011-12-0408</t>
         </is>
       </c>
       <c r="C839" t="inlineStr">
@@ -35610,7 +35610,7 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>2011-12-408</t>
+          <t>2011-12-0408</t>
         </is>
       </c>
       <c r="C840" t="inlineStr">
@@ -35652,7 +35652,7 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>2011-12-408</t>
+          <t>2011-12-0408</t>
         </is>
       </c>
       <c r="C841" t="inlineStr">
@@ -35694,7 +35694,7 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>2011-12-408</t>
+          <t>2011-12-0408</t>
         </is>
       </c>
       <c r="C842" t="inlineStr">
@@ -35736,7 +35736,7 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>2011-12-409</t>
+          <t>2011-12-0409</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
@@ -35778,7 +35778,7 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>2011-12-409</t>
+          <t>2011-12-0409</t>
         </is>
       </c>
       <c r="C844" t="inlineStr">
@@ -35820,7 +35820,7 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>2011-12-409</t>
+          <t>2011-12-0409</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
@@ -35862,7 +35862,7 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>2011-12-409</t>
+          <t>2011-12-0409</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
@@ -35904,7 +35904,7 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>2011-12-409</t>
+          <t>2011-12-0409</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
@@ -35946,7 +35946,7 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>2011-12-409</t>
+          <t>2011-12-0409</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
@@ -35988,7 +35988,7 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>2011-12-409</t>
+          <t>2011-12-0409</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
@@ -36030,7 +36030,7 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>2011-12-409</t>
+          <t>2011-12-0409</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
@@ -36072,7 +36072,7 @@
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>2011-12-409</t>
+          <t>2011-12-0409</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
@@ -36114,7 +36114,7 @@
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>2011-12-409</t>
+          <t>2011-12-0409</t>
         </is>
       </c>
       <c r="C852" t="inlineStr">
@@ -36156,7 +36156,7 @@
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>2011-12-410</t>
+          <t>2011-12-0410</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
@@ -36198,7 +36198,7 @@
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>2011-12-410</t>
+          <t>2011-12-0410</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
@@ -36240,7 +36240,7 @@
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>2011-12-410</t>
+          <t>2011-12-0410</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
@@ -36282,7 +36282,7 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>2011-12-410</t>
+          <t>2011-12-0410</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
@@ -36324,7 +36324,7 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>2011-12-410</t>
+          <t>2011-12-0410</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
@@ -36366,7 +36366,7 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>2011-12-410</t>
+          <t>2011-12-0410</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
@@ -36408,7 +36408,7 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>2011-12-411</t>
+          <t>2011-12-0411</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
@@ -36450,7 +36450,7 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>2011-12-411</t>
+          <t>2011-12-0411</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
@@ -36492,7 +36492,7 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>2011-12-411</t>
+          <t>2011-12-0411</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
@@ -36534,7 +36534,7 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>2011-12-411</t>
+          <t>2011-12-0411</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
@@ -36576,7 +36576,7 @@
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>2011-12-411</t>
+          <t>2011-12-0411</t>
         </is>
       </c>
       <c r="C863" t="inlineStr">
@@ -36618,7 +36618,7 @@
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>2011-12-411</t>
+          <t>2011-12-0411</t>
         </is>
       </c>
       <c r="C864" t="inlineStr">
@@ -36660,7 +36660,7 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>2011-12-411</t>
+          <t>2011-12-0411</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
@@ -36702,7 +36702,7 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>2011-12-411</t>
+          <t>2011-12-0411</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
@@ -36744,7 +36744,7 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>2011-12-411</t>
+          <t>2011-12-0411</t>
         </is>
       </c>
       <c r="C867" t="inlineStr">
@@ -36786,7 +36786,7 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>2011-12-411</t>
+          <t>2011-12-0411</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
@@ -36828,7 +36828,7 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>2011-12-411</t>
+          <t>2011-12-0411</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
@@ -36870,7 +36870,7 @@
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>2011-12-412</t>
+          <t>2011-12-0412</t>
         </is>
       </c>
       <c r="C870" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>2011-12-412</t>
+          <t>2011-12-0412</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
@@ -36954,7 +36954,7 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>2011-12-412</t>
+          <t>2011-12-0412</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
@@ -36996,7 +36996,7 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>2011-12-412</t>
+          <t>2011-12-0412</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
@@ -37038,7 +37038,7 @@
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>2011-12-412</t>
+          <t>2011-12-0412</t>
         </is>
       </c>
       <c r="C874" t="inlineStr">
@@ -37080,7 +37080,7 @@
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>2011-12-413</t>
+          <t>2011-12-0413</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
@@ -37122,7 +37122,7 @@
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>2011-12-413</t>
+          <t>2011-12-0413</t>
         </is>
       </c>
       <c r="C876" t="inlineStr">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>2011-12-413</t>
+          <t>2011-12-0413</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
@@ -37206,7 +37206,7 @@
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>2011-12-413</t>
+          <t>2011-12-0413</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
@@ -37248,7 +37248,7 @@
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>2011-12-413</t>
+          <t>2011-12-0413</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
@@ -37290,7 +37290,7 @@
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>2011-12-413</t>
+          <t>2011-12-0413</t>
         </is>
       </c>
       <c r="C880" t="inlineStr">
@@ -37332,7 +37332,7 @@
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>2011-12-413</t>
+          <t>2011-12-0413</t>
         </is>
       </c>
       <c r="C881" t="inlineStr">
@@ -37374,7 +37374,7 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>2011-12-413</t>
+          <t>2011-12-0413</t>
         </is>
       </c>
       <c r="C882" t="inlineStr">
@@ -37416,7 +37416,7 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>2011-12-413</t>
+          <t>2011-12-0413</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
@@ -37458,7 +37458,7 @@
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>2011-12-413</t>
+          <t>2011-12-0413</t>
         </is>
       </c>
       <c r="C884" t="inlineStr">
@@ -37500,7 +37500,7 @@
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>2011-12-413</t>
+          <t>2011-12-0413</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
@@ -37542,7 +37542,7 @@
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>2011-12-413</t>
+          <t>2011-12-0413</t>
         </is>
       </c>
       <c r="C886" t="inlineStr">
@@ -37584,7 +37584,7 @@
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>2011-12-414</t>
+          <t>2011-12-0414</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
@@ -37626,7 +37626,7 @@
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>2011-12-414</t>
+          <t>2011-12-0414</t>
         </is>
       </c>
       <c r="C888" t="inlineStr">
@@ -37668,7 +37668,7 @@
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>2011-12-414</t>
+          <t>2011-12-0414</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
@@ -37710,7 +37710,7 @@
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>2011-12-414</t>
+          <t>2011-12-0414</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
@@ -37752,7 +37752,7 @@
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>2011-12-414</t>
+          <t>2011-12-0414</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
@@ -37794,7 +37794,7 @@
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>2011-12-414</t>
+          <t>2011-12-0414</t>
         </is>
       </c>
       <c r="C892" t="inlineStr">
@@ -37836,7 +37836,7 @@
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>2011-12-414</t>
+          <t>2011-12-0414</t>
         </is>
       </c>
       <c r="C893" t="inlineStr">
@@ -37878,7 +37878,7 @@
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>2011-12-415</t>
+          <t>2011-12-0415</t>
         </is>
       </c>
       <c r="C894" t="inlineStr">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>2011-12-415</t>
+          <t>2011-12-0415</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
@@ -37962,7 +37962,7 @@
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>2011-12-415</t>
+          <t>2011-12-0415</t>
         </is>
       </c>
       <c r="C896" t="inlineStr">
@@ -38004,7 +38004,7 @@
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>2011-12-415</t>
+          <t>2011-12-0415</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>2011-12-415</t>
+          <t>2011-12-0415</t>
         </is>
       </c>
       <c r="C898" t="inlineStr">
@@ -38088,7 +38088,7 @@
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>2011-12-415</t>
+          <t>2011-12-0415</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
@@ -38130,7 +38130,7 @@
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>2011-12-415</t>
+          <t>2011-12-0415</t>
         </is>
       </c>
       <c r="C900" t="inlineStr">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>2011-12-415</t>
+          <t>2011-12-0415</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
@@ -38214,7 +38214,7 @@
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>2011-12-415</t>
+          <t>2011-12-0415</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
@@ -38256,7 +38256,7 @@
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>2011-12-416</t>
+          <t>2011-12-0416</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
@@ -38298,7 +38298,7 @@
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>2011-12-416</t>
+          <t>2011-12-0416</t>
         </is>
       </c>
       <c r="C904" t="inlineStr">
@@ -38340,7 +38340,7 @@
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>2011-12-416</t>
+          <t>2011-12-0416</t>
         </is>
       </c>
       <c r="C905" t="inlineStr">
@@ -38382,7 +38382,7 @@
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>2011-12-416</t>
+          <t>2011-12-0416</t>
         </is>
       </c>
       <c r="C906" t="inlineStr">
@@ -38424,7 +38424,7 @@
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>2011-12-416</t>
+          <t>2011-12-0416</t>
         </is>
       </c>
       <c r="C907" t="inlineStr">
@@ -38466,7 +38466,7 @@
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>2011-12-416</t>
+          <t>2011-12-0416</t>
         </is>
       </c>
       <c r="C908" t="inlineStr">
@@ -38508,7 +38508,7 @@
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>2011-12-416</t>
+          <t>2011-12-0416</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
@@ -38550,7 +38550,7 @@
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>2011-12-416</t>
+          <t>2011-12-0416</t>
         </is>
       </c>
       <c r="C910" t="inlineStr">
@@ -38592,7 +38592,7 @@
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>2011-12-416</t>
+          <t>2011-12-0416</t>
         </is>
       </c>
       <c r="C911" t="inlineStr">
@@ -38634,7 +38634,7 @@
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>2011-12-416</t>
+          <t>2011-12-0416</t>
         </is>
       </c>
       <c r="C912" t="inlineStr">
@@ -38676,7 +38676,7 @@
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>2011-12-416</t>
+          <t>2011-12-0416</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
@@ -38718,7 +38718,7 @@
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>2011-12-417</t>
+          <t>2011-12-0417</t>
         </is>
       </c>
       <c r="C914" t="inlineStr">
@@ -38760,7 +38760,7 @@
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>2011-12-417</t>
+          <t>2011-12-0417</t>
         </is>
       </c>
       <c r="C915" t="inlineStr">
@@ -38802,7 +38802,7 @@
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>2011-12-417</t>
+          <t>2011-12-0417</t>
         </is>
       </c>
       <c r="C916" t="inlineStr">
@@ -38844,7 +38844,7 @@
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>2011-12-417</t>
+          <t>2011-12-0417</t>
         </is>
       </c>
       <c r="C917" t="inlineStr">
@@ -38886,7 +38886,7 @@
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>2011-12-417</t>
+          <t>2011-12-0417</t>
         </is>
       </c>
       <c r="C918" t="inlineStr">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>2011-12-418</t>
+          <t>2011-12-0418</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
@@ -38970,7 +38970,7 @@
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>2011-12-418</t>
+          <t>2011-12-0418</t>
         </is>
       </c>
       <c r="C920" t="inlineStr">
@@ -39012,7 +39012,7 @@
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>2011-12-418</t>
+          <t>2011-12-0418</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
@@ -39054,7 +39054,7 @@
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>2011-12-418</t>
+          <t>2011-12-0418</t>
         </is>
       </c>
       <c r="C922" t="inlineStr">
@@ -39096,7 +39096,7 @@
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>2011-12-418</t>
+          <t>2011-12-0418</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
@@ -39138,7 +39138,7 @@
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>2011-12-418</t>
+          <t>2011-12-0418</t>
         </is>
       </c>
       <c r="C924" t="inlineStr">
@@ -39180,7 +39180,7 @@
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>2011-12-418</t>
+          <t>2011-12-0418</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
@@ -39222,7 +39222,7 @@
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>2011-12-418</t>
+          <t>2011-12-0418</t>
         </is>
       </c>
       <c r="C926" t="inlineStr">
@@ -39264,7 +39264,7 @@
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>2011-12-418</t>
+          <t>2011-12-0418</t>
         </is>
       </c>
       <c r="C927" t="inlineStr">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>2011-12-418</t>
+          <t>2011-12-0418</t>
         </is>
       </c>
       <c r="C928" t="inlineStr">
@@ -39348,7 +39348,7 @@
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>2011-12-418</t>
+          <t>2011-12-0418</t>
         </is>
       </c>
       <c r="C929" t="inlineStr">
@@ -39390,7 +39390,7 @@
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>2011-12-418</t>
+          <t>2011-12-0418</t>
         </is>
       </c>
       <c r="C930" t="inlineStr">
@@ -39432,7 +39432,7 @@
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>2011-12-418</t>
+          <t>2011-12-0418</t>
         </is>
       </c>
       <c r="C931" t="inlineStr">
@@ -39474,7 +39474,7 @@
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t>2011-12-418</t>
+          <t>2011-12-0418</t>
         </is>
       </c>
       <c r="C932" t="inlineStr">
@@ -39516,7 +39516,7 @@
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>2011-12-419</t>
+          <t>2011-12-0419</t>
         </is>
       </c>
       <c r="C933" t="inlineStr">
@@ -39558,7 +39558,7 @@
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>2011-12-419</t>
+          <t>2011-12-0419</t>
         </is>
       </c>
       <c r="C934" t="inlineStr">
@@ -39600,7 +39600,7 @@
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>2011-12-419</t>
+          <t>2011-12-0419</t>
         </is>
       </c>
       <c r="C935" t="inlineStr">
@@ -39642,7 +39642,7 @@
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>2011-12-419</t>
+          <t>2011-12-0419</t>
         </is>
       </c>
       <c r="C936" t="inlineStr">
@@ -39684,7 +39684,7 @@
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>2011-12-419</t>
+          <t>2011-12-0419</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
@@ -39726,7 +39726,7 @@
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>2011-12-420</t>
+          <t>2011-12-0420</t>
         </is>
       </c>
       <c r="C938" t="inlineStr">
@@ -39768,7 +39768,7 @@
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>2011-12-420</t>
+          <t>2011-12-0420</t>
         </is>
       </c>
       <c r="C939" t="inlineStr">
@@ -39810,7 +39810,7 @@
       </c>
       <c r="B940" t="inlineStr">
         <is>
-          <t>2011-12-420</t>
+          <t>2011-12-0420</t>
         </is>
       </c>
       <c r="C940" t="inlineStr">
@@ -39852,7 +39852,7 @@
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>2011-12-420</t>
+          <t>2011-12-0420</t>
         </is>
       </c>
       <c r="C941" t="inlineStr">
@@ -39894,7 +39894,7 @@
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>2011-12-420</t>
+          <t>2011-12-0420</t>
         </is>
       </c>
       <c r="C942" t="inlineStr">
@@ -39936,7 +39936,7 @@
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>2011-12-420</t>
+          <t>2011-12-0420</t>
         </is>
       </c>
       <c r="C943" t="inlineStr">
@@ -39978,7 +39978,7 @@
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>2011-12-421</t>
+          <t>2011-12-0421</t>
         </is>
       </c>
       <c r="C944" t="inlineStr">
@@ -40020,7 +40020,7 @@
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>2011-12-421</t>
+          <t>2011-12-0421</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
@@ -40062,7 +40062,7 @@
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>2011-12-421</t>
+          <t>2011-12-0421</t>
         </is>
       </c>
       <c r="C946" t="inlineStr">
@@ -40104,7 +40104,7 @@
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>2011-12-421</t>
+          <t>2011-12-0421</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
@@ -40146,7 +40146,7 @@
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>2011-12-421</t>
+          <t>2011-12-0421</t>
         </is>
       </c>
       <c r="C948" t="inlineStr">
@@ -40188,7 +40188,7 @@
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t>2011-12-421</t>
+          <t>2011-12-0421</t>
         </is>
       </c>
       <c r="C949" t="inlineStr">
@@ -40230,7 +40230,7 @@
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>2011-12-421</t>
+          <t>2011-12-0421</t>
         </is>
       </c>
       <c r="C950" t="inlineStr">
@@ -40272,7 +40272,7 @@
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>2011-12-421</t>
+          <t>2011-12-0421</t>
         </is>
       </c>
       <c r="C951" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="B952" t="inlineStr">
         <is>
-          <t>2011-12-422</t>
+          <t>2011-12-0422</t>
         </is>
       </c>
       <c r="C952" t="inlineStr">
@@ -40356,7 +40356,7 @@
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>2011-12-422</t>
+          <t>2011-12-0422</t>
         </is>
       </c>
       <c r="C953" t="inlineStr">
@@ -40398,7 +40398,7 @@
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t>2011-12-422</t>
+          <t>2011-12-0422</t>
         </is>
       </c>
       <c r="C954" t="inlineStr">
@@ -40440,7 +40440,7 @@
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>2011-12-422</t>
+          <t>2011-12-0422</t>
         </is>
       </c>
       <c r="C955" t="inlineStr">
@@ -40482,7 +40482,7 @@
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t>2011-12-422</t>
+          <t>2011-12-0422</t>
         </is>
       </c>
       <c r="C956" t="inlineStr">
@@ -40524,7 +40524,7 @@
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>2011-12-422</t>
+          <t>2011-12-0422</t>
         </is>
       </c>
       <c r="C957" t="inlineStr">
@@ -40566,7 +40566,7 @@
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t>2011-12-422</t>
+          <t>2011-12-0422</t>
         </is>
       </c>
       <c r="C958" t="inlineStr">
@@ -40608,7 +40608,7 @@
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>2011-12-422</t>
+          <t>2011-12-0422</t>
         </is>
       </c>
       <c r="C959" t="inlineStr">
@@ -40650,7 +40650,7 @@
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t>2011-12-422</t>
+          <t>2011-12-0422</t>
         </is>
       </c>
       <c r="C960" t="inlineStr">
@@ -40692,7 +40692,7 @@
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>2011-12-423</t>
+          <t>2011-12-0423</t>
         </is>
       </c>
       <c r="C961" t="inlineStr">
@@ -40734,7 +40734,7 @@
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t>2011-12-423</t>
+          <t>2011-12-0423</t>
         </is>
       </c>
       <c r="C962" t="inlineStr">
@@ -40776,7 +40776,7 @@
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>2011-12-423</t>
+          <t>2011-12-0423</t>
         </is>
       </c>
       <c r="C963" t="inlineStr">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t>2011-12-423</t>
+          <t>2011-12-0423</t>
         </is>
       </c>
       <c r="C964" t="inlineStr">
@@ -40860,7 +40860,7 @@
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>2011-12-423</t>
+          <t>2011-12-0423</t>
         </is>
       </c>
       <c r="C965" t="inlineStr">
@@ -40902,7 +40902,7 @@
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>2011-12-423</t>
+          <t>2011-12-0423</t>
         </is>
       </c>
       <c r="C966" t="inlineStr">
@@ -40944,7 +40944,7 @@
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>2011-12-424</t>
+          <t>2011-12-0424</t>
         </is>
       </c>
       <c r="C967" t="inlineStr">
@@ -40986,7 +40986,7 @@
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t>2011-12-424</t>
+          <t>2011-12-0424</t>
         </is>
       </c>
       <c r="C968" t="inlineStr">
@@ -41028,7 +41028,7 @@
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>2011-12-424</t>
+          <t>2011-12-0424</t>
         </is>
       </c>
       <c r="C969" t="inlineStr">
@@ -41070,7 +41070,7 @@
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t>2011-12-424</t>
+          <t>2011-12-0424</t>
         </is>
       </c>
       <c r="C970" t="inlineStr">
@@ -41112,7 +41112,7 @@
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>2011-12-424</t>
+          <t>2011-12-0424</t>
         </is>
       </c>
       <c r="C971" t="inlineStr">
@@ -41154,7 +41154,7 @@
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t>2011-12-425</t>
+          <t>2011-12-0425</t>
         </is>
       </c>
       <c r="C972" t="inlineStr">
@@ -41196,7 +41196,7 @@
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t>2011-12-425</t>
+          <t>2011-12-0425</t>
         </is>
       </c>
       <c r="C973" t="inlineStr">
@@ -41238,7 +41238,7 @@
       </c>
       <c r="B974" t="inlineStr">
         <is>
-          <t>2011-12-425</t>
+          <t>2011-12-0425</t>
         </is>
       </c>
       <c r="C974" t="inlineStr">
@@ -41280,7 +41280,7 @@
       </c>
       <c r="B975" t="inlineStr">
         <is>
-          <t>2011-12-425</t>
+          <t>2011-12-0425</t>
         </is>
       </c>
       <c r="C975" t="inlineStr">
@@ -41322,7 +41322,7 @@
       </c>
       <c r="B976" t="inlineStr">
         <is>
-          <t>2011-12-425</t>
+          <t>2011-12-0425</t>
         </is>
       </c>
       <c r="C976" t="inlineStr">
@@ -41364,7 +41364,7 @@
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>2011-12-425</t>
+          <t>2011-12-0425</t>
         </is>
       </c>
       <c r="C977" t="inlineStr">
@@ -41406,7 +41406,7 @@
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t>2011-12-425</t>
+          <t>2011-12-0425</t>
         </is>
       </c>
       <c r="C978" t="inlineStr">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>2011-12-426</t>
+          <t>2011-12-0426</t>
         </is>
       </c>
       <c r="C979" t="inlineStr">
@@ -41490,7 +41490,7 @@
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>2011-12-426</t>
+          <t>2011-12-0426</t>
         </is>
       </c>
       <c r="C980" t="inlineStr">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>2011-12-426</t>
+          <t>2011-12-0426</t>
         </is>
       </c>
       <c r="C981" t="inlineStr">
@@ -41574,7 +41574,7 @@
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t>2011-12-426</t>
+          <t>2011-12-0426</t>
         </is>
       </c>
       <c r="C982" t="inlineStr">
@@ -41616,7 +41616,7 @@
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>2011-12-426</t>
+          <t>2011-12-0426</t>
         </is>
       </c>
       <c r="C983" t="inlineStr">
@@ -41658,7 +41658,7 @@
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t>2011-12-426</t>
+          <t>2011-12-0426</t>
         </is>
       </c>
       <c r="C984" t="inlineStr">
@@ -41700,7 +41700,7 @@
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>2011-12-426</t>
+          <t>2011-12-0426</t>
         </is>
       </c>
       <c r="C985" t="inlineStr">
@@ -41742,7 +41742,7 @@
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t>2011-12-426</t>
+          <t>2011-12-0426</t>
         </is>
       </c>
       <c r="C986" t="inlineStr">
@@ -41784,7 +41784,7 @@
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>2011-12-426</t>
+          <t>2011-12-0426</t>
         </is>
       </c>
       <c r="C987" t="inlineStr">
@@ -41826,7 +41826,7 @@
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t>2011-12-426</t>
+          <t>2011-12-0426</t>
         </is>
       </c>
       <c r="C988" t="inlineStr">
@@ -41868,7 +41868,7 @@
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>2011-12-426</t>
+          <t>2011-12-0426</t>
         </is>
       </c>
       <c r="C989" t="inlineStr">
@@ -41910,7 +41910,7 @@
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t>2011-12-426</t>
+          <t>2011-12-0426</t>
         </is>
       </c>
       <c r="C990" t="inlineStr">
@@ -41952,7 +41952,7 @@
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>2011-12-426</t>
+          <t>2011-12-0426</t>
         </is>
       </c>
       <c r="C991" t="inlineStr">
@@ -41994,7 +41994,7 @@
       </c>
       <c r="B992" t="inlineStr">
         <is>
-          <t>2011-12-428</t>
+          <t>2011-12-0428</t>
         </is>
       </c>
       <c r="C992" t="inlineStr">
@@ -42036,7 +42036,7 @@
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t>2011-12-428</t>
+          <t>2011-12-0428</t>
         </is>
       </c>
       <c r="C993" t="inlineStr">
@@ -42078,7 +42078,7 @@
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t>2011-12-428</t>
+          <t>2011-12-0428</t>
         </is>
       </c>
       <c r="C994" t="inlineStr">
@@ -42120,7 +42120,7 @@
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>2011-12-428</t>
+          <t>2011-12-0428</t>
         </is>
       </c>
       <c r="C995" t="inlineStr">
@@ -42162,7 +42162,7 @@
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>2011-12-429</t>
+          <t>2011-12-0429</t>
         </is>
       </c>
       <c r="C996" t="inlineStr">
@@ -42204,7 +42204,7 @@
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>2011-12-429</t>
+          <t>2011-12-0429</t>
         </is>
       </c>
       <c r="C997" t="inlineStr">
@@ -42246,7 +42246,7 @@
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t>2011-12-429</t>
+          <t>2011-12-0429</t>
         </is>
       </c>
       <c r="C998" t="inlineStr">
@@ -42288,7 +42288,7 @@
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>2011-12-429</t>
+          <t>2011-12-0429</t>
         </is>
       </c>
       <c r="C999" t="inlineStr">
@@ -42330,7 +42330,7 @@
       </c>
       <c r="B1000" t="inlineStr">
         <is>
-          <t>2011-12-430</t>
+          <t>2011-12-0430</t>
         </is>
       </c>
       <c r="C1000" t="inlineStr">
@@ -42372,7 +42372,7 @@
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>2011-12-430</t>
+          <t>2011-12-0430</t>
         </is>
       </c>
       <c r="C1001" t="inlineStr">
@@ -42414,7 +42414,7 @@
       </c>
       <c r="B1002" t="inlineStr">
         <is>
-          <t>2011-12-430</t>
+          <t>2011-12-0430</t>
         </is>
       </c>
       <c r="C1002" t="inlineStr">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t>2011-12-501</t>
+          <t>2011-12-0501</t>
         </is>
       </c>
       <c r="C1003" t="inlineStr">
@@ -42498,7 +42498,7 @@
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t>2011-12-501</t>
+          <t>2011-12-0501</t>
         </is>
       </c>
       <c r="C1004" t="inlineStr">
@@ -42540,7 +42540,7 @@
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>2011-12-501</t>
+          <t>2011-12-0501</t>
         </is>
       </c>
       <c r="C1005" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="B1006" t="inlineStr">
         <is>
-          <t>2011-12-502</t>
+          <t>2011-12-0502</t>
         </is>
       </c>
       <c r="C1006" t="inlineStr">
@@ -42624,7 +42624,7 @@
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>2011-12-502</t>
+          <t>2011-12-0502</t>
         </is>
       </c>
       <c r="C1007" t="inlineStr">
@@ -42666,7 +42666,7 @@
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t>2011-12-502</t>
+          <t>2011-12-0502</t>
         </is>
       </c>
       <c r="C1008" t="inlineStr">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t>2011-12-503</t>
+          <t>2011-12-0503</t>
         </is>
       </c>
       <c r="C1009" t="inlineStr">
@@ -42750,7 +42750,7 @@
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t>2011-12-503</t>
+          <t>2011-12-0503</t>
         </is>
       </c>
       <c r="C1010" t="inlineStr">
@@ -42792,7 +42792,7 @@
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t>2011-12-504</t>
+          <t>2011-12-0504</t>
         </is>
       </c>
       <c r="C1011" t="inlineStr">
@@ -42834,7 +42834,7 @@
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t>2011-12-504</t>
+          <t>2011-12-0504</t>
         </is>
       </c>
       <c r="C1012" t="inlineStr">
@@ -42876,7 +42876,7 @@
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t>2011-12-504</t>
+          <t>2011-12-0504</t>
         </is>
       </c>
       <c r="C1013" t="inlineStr">
@@ -42918,7 +42918,7 @@
       </c>
       <c r="B1014" t="inlineStr">
         <is>
-          <t>2011-12-505</t>
+          <t>2011-12-0505</t>
         </is>
       </c>
       <c r="C1014" t="inlineStr">
@@ -42960,7 +42960,7 @@
       </c>
       <c r="B1015" t="inlineStr">
         <is>
-          <t>2011-12-505</t>
+          <t>2011-12-0505</t>
         </is>
       </c>
       <c r="C1015" t="inlineStr">
@@ -43002,7 +43002,7 @@
       </c>
       <c r="B1016" t="inlineStr">
         <is>
-          <t>2011-12-505</t>
+          <t>2011-12-0505</t>
         </is>
       </c>
       <c r="C1016" t="inlineStr">
@@ -43044,7 +43044,7 @@
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t>2011-12-505</t>
+          <t>2011-12-0505</t>
         </is>
       </c>
       <c r="C1017" t="inlineStr">
@@ -43086,7 +43086,7 @@
       </c>
       <c r="B1018" t="inlineStr">
         <is>
-          <t>2011-12-506</t>
+          <t>2011-12-0506</t>
         </is>
       </c>
       <c r="C1018" t="inlineStr">
@@ -43128,7 +43128,7 @@
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t>2011-12-506</t>
+          <t>2011-12-0506</t>
         </is>
       </c>
       <c r="C1019" t="inlineStr">
@@ -43170,7 +43170,7 @@
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t>2011-12-506</t>
+          <t>2011-12-0506</t>
         </is>
       </c>
       <c r="C1020" t="inlineStr">
@@ -43212,7 +43212,7 @@
       </c>
       <c r="B1021" t="inlineStr">
         <is>
-          <t>2011-12-506</t>
+          <t>2011-12-0506</t>
         </is>
       </c>
       <c r="C1021" t="inlineStr">
@@ -43254,7 +43254,7 @@
       </c>
       <c r="B1022" t="inlineStr">
         <is>
-          <t>2011-12-507</t>
+          <t>2011-12-0507</t>
         </is>
       </c>
       <c r="C1022" t="inlineStr">
@@ -43296,7 +43296,7 @@
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t>2011-12-507</t>
+          <t>2011-12-0507</t>
         </is>
       </c>
       <c r="C1023" t="inlineStr">
@@ -43338,7 +43338,7 @@
       </c>
       <c r="B1024" t="inlineStr">
         <is>
-          <t>2011-12-508</t>
+          <t>2011-12-0508</t>
         </is>
       </c>
       <c r="C1024" t="inlineStr">
@@ -43380,7 +43380,7 @@
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t>2011-12-508</t>
+          <t>2011-12-0508</t>
         </is>
       </c>
       <c r="C1025" t="inlineStr">
@@ -43422,7 +43422,7 @@
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t>2011-12-508</t>
+          <t>2011-12-0508</t>
         </is>
       </c>
       <c r="C1026" t="inlineStr">
@@ -43464,7 +43464,7 @@
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t>2011-12-508</t>
+          <t>2011-12-0508</t>
         </is>
       </c>
       <c r="C1027" t="inlineStr">
@@ -43506,7 +43506,7 @@
       </c>
       <c r="B1028" t="inlineStr">
         <is>
-          <t>2011-12-509</t>
+          <t>2011-12-0509</t>
         </is>
       </c>
       <c r="C1028" t="inlineStr">
@@ -43548,7 +43548,7 @@
       </c>
       <c r="B1029" t="inlineStr">
         <is>
-          <t>2011-12-509</t>
+          <t>2011-12-0509</t>
         </is>
       </c>
       <c r="C1029" t="inlineStr">
@@ -43590,7 +43590,7 @@
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t>2011-12-510</t>
+          <t>2011-12-0510</t>
         </is>
       </c>
       <c r="C1030" t="inlineStr">
@@ -43632,7 +43632,7 @@
       </c>
       <c r="B1031" t="inlineStr">
         <is>
-          <t>2011-12-510</t>
+          <t>2011-12-0510</t>
         </is>
       </c>
       <c r="C1031" t="inlineStr">
@@ -43674,7 +43674,7 @@
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t>2011-12-510</t>
+          <t>2011-12-0510</t>
         </is>
       </c>
       <c r="C1032" t="inlineStr">
@@ -43716,7 +43716,7 @@
       </c>
       <c r="B1033" t="inlineStr">
         <is>
-          <t>2011-12-511</t>
+          <t>2011-12-0511</t>
         </is>
       </c>
       <c r="C1033" t="inlineStr">
@@ -43758,7 +43758,7 @@
       </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t>2011-12-512</t>
+          <t>2011-12-0512</t>
         </is>
       </c>
       <c r="C1034" t="inlineStr">
@@ -43800,7 +43800,7 @@
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t>2011-12-512</t>
+          <t>2011-12-0512</t>
         </is>
       </c>
       <c r="C1035" t="inlineStr">
@@ -43842,7 +43842,7 @@
       </c>
       <c r="B1036" t="inlineStr">
         <is>
-          <t>2011-12-513</t>
+          <t>2011-12-0513</t>
         </is>
       </c>
       <c r="C1036" t="inlineStr">
@@ -43884,7 +43884,7 @@
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t>2011-12-513</t>
+          <t>2011-12-0513</t>
         </is>
       </c>
       <c r="C1037" t="inlineStr">
@@ -43926,7 +43926,7 @@
       </c>
       <c r="B1038" t="inlineStr">
         <is>
-          <t>2011-12-514</t>
+          <t>2011-12-0514</t>
         </is>
       </c>
       <c r="C1038" t="inlineStr">
@@ -43968,7 +43968,7 @@
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t>2011-12-514</t>
+          <t>2011-12-0514</t>
         </is>
       </c>
       <c r="C1039" t="inlineStr">
@@ -44010,7 +44010,7 @@
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t>2011-12-515</t>
+          <t>2011-12-0515</t>
         </is>
       </c>
       <c r="C1040" t="inlineStr">
@@ -44052,7 +44052,7 @@
       </c>
       <c r="B1041" t="inlineStr">
         <is>
-          <t>2011-12-515</t>
+          <t>2011-12-0515</t>
         </is>
       </c>
       <c r="C1041" t="inlineStr">
@@ -44094,7 +44094,7 @@
       </c>
       <c r="B1042" t="inlineStr">
         <is>
-          <t>2011-12-516</t>
+          <t>2011-12-0516</t>
         </is>
       </c>
       <c r="C1042" t="inlineStr">
@@ -44136,7 +44136,7 @@
       </c>
       <c r="B1043" t="inlineStr">
         <is>
-          <t>2011-12-516</t>
+          <t>2011-12-0516</t>
         </is>
       </c>
       <c r="C1043" t="inlineStr">
@@ -44178,7 +44178,7 @@
       </c>
       <c r="B1044" t="inlineStr">
         <is>
-          <t>2011-12-517</t>
+          <t>2011-12-0517</t>
         </is>
       </c>
       <c r="C1044" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t>2011-12-517</t>
+          <t>2011-12-0517</t>
         </is>
       </c>
       <c r="C1045" t="inlineStr">
@@ -44262,7 +44262,7 @@
       </c>
       <c r="B1046" t="inlineStr">
         <is>
-          <t>2011-12-518</t>
+          <t>2011-12-0518</t>
         </is>
       </c>
       <c r="C1046" t="inlineStr">
@@ -44304,7 +44304,7 @@
       </c>
       <c r="B1047" t="inlineStr">
         <is>
-          <t>2011-12-518</t>
+          <t>2011-12-0518</t>
         </is>
       </c>
       <c r="C1047" t="inlineStr">
@@ -44346,7 +44346,7 @@
       </c>
       <c r="B1048" t="inlineStr">
         <is>
-          <t>2011-12-519</t>
+          <t>2011-12-0519</t>
         </is>
       </c>
       <c r="C1048" t="inlineStr">
@@ -44388,7 +44388,7 @@
       </c>
       <c r="B1049" t="inlineStr">
         <is>
-          <t>2011-12-519</t>
+          <t>2011-12-0519</t>
         </is>
       </c>
       <c r="C1049" t="inlineStr">
@@ -44430,7 +44430,7 @@
       </c>
       <c r="B1050" t="inlineStr">
         <is>
-          <t>2011-12-520</t>
+          <t>2011-12-0520</t>
         </is>
       </c>
       <c r="C1050" t="inlineStr">
@@ -44472,7 +44472,7 @@
       </c>
       <c r="B1051" t="inlineStr">
         <is>
-          <t>2011-12-520</t>
+          <t>2011-12-0520</t>
         </is>
       </c>
       <c r="C1051" t="inlineStr">
@@ -44514,7 +44514,7 @@
       </c>
       <c r="B1052" t="inlineStr">
         <is>
-          <t>2011-12-521</t>
+          <t>2011-12-0521</t>
         </is>
       </c>
       <c r="C1052" t="inlineStr">
@@ -44556,7 +44556,7 @@
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t>2011-12-521</t>
+          <t>2011-12-0521</t>
         </is>
       </c>
       <c r="C1053" t="inlineStr">
@@ -44598,7 +44598,7 @@
       </c>
       <c r="B1054" t="inlineStr">
         <is>
-          <t>2011-12-522</t>
+          <t>2011-12-0522</t>
         </is>
       </c>
       <c r="C1054" t="inlineStr">
@@ -44640,7 +44640,7 @@
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t>2011-12-523</t>
+          <t>2011-12-0523</t>
         </is>
       </c>
       <c r="C1055" t="inlineStr">
@@ -44682,7 +44682,7 @@
       </c>
       <c r="B1056" t="inlineStr">
         <is>
-          <t>2011-12-524</t>
+          <t>2011-12-0524</t>
         </is>
       </c>
       <c r="C1056" t="inlineStr">
@@ -44724,7 +44724,7 @@
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t>2011-12-526</t>
+          <t>2011-12-0526</t>
         </is>
       </c>
       <c r="C1057" t="inlineStr">
@@ -44766,7 +44766,7 @@
       </c>
       <c r="B1058" t="inlineStr">
         <is>
-          <t>2011-12-527</t>
+          <t>2011-12-0527</t>
         </is>
       </c>
       <c r="C1058" t="inlineStr">
@@ -44808,7 +44808,7 @@
       </c>
       <c r="B1059" t="inlineStr">
         <is>
-          <t>2011-12-528</t>
+          <t>2011-12-0528</t>
         </is>
       </c>
       <c r="C1059" t="inlineStr">
@@ -44850,7 +44850,7 @@
       </c>
       <c r="B1060" t="inlineStr">
         <is>
-          <t>2011-12-529</t>
+          <t>2011-12-0529</t>
         </is>
       </c>
       <c r="C1060" t="inlineStr">
@@ -44892,7 +44892,7 @@
       </c>
       <c r="B1061" t="inlineStr">
         <is>
-          <t>2011-12-530</t>
+          <t>2011-12-0530</t>
         </is>
       </c>
       <c r="C1061" t="inlineStr">
@@ -44934,7 +44934,7 @@
       </c>
       <c r="B1062" t="inlineStr">
         <is>
-          <t>2011-12-531</t>
+          <t>2011-12-0531</t>
         </is>
       </c>
       <c r="C1062" t="inlineStr">
@@ -44976,7 +44976,7 @@
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t>2011-12-601</t>
+          <t>2011-12-0601</t>
         </is>
       </c>
       <c r="C1063" t="inlineStr">
@@ -45018,7 +45018,7 @@
       </c>
       <c r="B1064" t="inlineStr">
         <is>
-          <t>2011-12-602</t>
+          <t>2011-12-0602</t>
         </is>
       </c>
       <c r="C1064" t="inlineStr">
@@ -45060,7 +45060,7 @@
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t>2011-12-603</t>
+          <t>2011-12-0603</t>
         </is>
       </c>
       <c r="C1065" t="inlineStr">
@@ -45102,7 +45102,7 @@
       </c>
       <c r="B1066" t="inlineStr">
         <is>
-          <t>2011-12-604</t>
+          <t>2011-12-0604</t>
         </is>
       </c>
       <c r="C1066" t="inlineStr">
@@ -45144,7 +45144,7 @@
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t>2011-12-605</t>
+          <t>2011-12-0605</t>
         </is>
       </c>
       <c r="C1067" t="inlineStr">
@@ -45186,7 +45186,7 @@
       </c>
       <c r="B1068" t="inlineStr">
         <is>
-          <t>2011-12-606</t>
+          <t>2011-12-0606</t>
         </is>
       </c>
       <c r="C1068" t="inlineStr">
@@ -45228,7 +45228,7 @@
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t>2011-12-607</t>
+          <t>2011-12-0607</t>
         </is>
       </c>
       <c r="C1069" t="inlineStr">
@@ -45270,7 +45270,7 @@
       </c>
       <c r="B1070" t="inlineStr">
         <is>
-          <t>2011-12-609</t>
+          <t>2011-12-0609</t>
         </is>
       </c>
       <c r="C1070" t="inlineStr">
@@ -45312,7 +45312,7 @@
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t>2011-12-612</t>
+          <t>2011-12-0612</t>
         </is>
       </c>
       <c r="C1071" t="inlineStr">
@@ -45354,7 +45354,7 @@
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t>2011-12-614</t>
+          <t>2011-12-0614</t>
         </is>
       </c>
       <c r="C1072" t="inlineStr">
@@ -45396,7 +45396,7 @@
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t>2011-12-617</t>
+          <t>2011-12-0617</t>
         </is>
       </c>
       <c r="C1073" t="inlineStr">
@@ -45438,7 +45438,7 @@
       </c>
       <c r="B1074" t="inlineStr">
         <is>
-          <t>2011-12-619</t>
+          <t>2011-12-0619</t>
         </is>
       </c>
       <c r="C1074" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t>2011-12-621</t>
+          <t>2011-12-0621</t>
         </is>
       </c>
       <c r="C1075" t="inlineStr">

--- a/Odds-Data-Clean/2011-12.xlsx
+++ b/Odds-Data-Clean/2011-12.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -54,18 +54,18 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
@@ -543,7 +543,11 @@
           <t>2011-12-1225</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Orlando Magic</t>
@@ -838,7 +842,11 @@
           <t>Minnesota Timberwolves</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E12" t="n">
         <v>209</v>
       </c>
@@ -1548,7 +1556,11 @@
           <t>Memphis Grizzlies</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E29" t="n">
         <v>195</v>
       </c>
@@ -1833,7 +1845,11 @@
           <t>2011-12-1229</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
           <t>Dallas Mavericks</t>
@@ -2627,7 +2643,11 @@
           <t>2011-12-1231</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
           <t>Phoenix Suns</t>
@@ -3426,7 +3446,11 @@
           <t>Dallas Mavericks</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E74" t="n">
         <v>199.5</v>
       </c>
@@ -3585,7 +3609,11 @@
           <t>2011-12-0103</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
           <t>Portland Trail Blazers</t>
@@ -4715,7 +4743,11 @@
           <t>2011-12-0106</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr"/>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D105" t="inlineStr">
         <is>
           <t>Houston Rockets</t>
@@ -5178,7 +5210,11 @@
           <t>Houston Rockets</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E116" t="n">
         <v>202.5</v>
       </c>
@@ -5463,7 +5499,11 @@
           <t>2011-12-0108</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr"/>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D123" t="inlineStr">
         <is>
           <t>San Antonio Spurs</t>
@@ -6094,7 +6134,11 @@
           <t>Memphis Grizzlies</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E138" t="n">
         <v>193</v>
       </c>
@@ -6510,7 +6554,11 @@
           <t>New Orleans Pelicans</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E148" t="n">
         <v>187</v>
       </c>
@@ -7677,7 +7725,11 @@
           <t>2011-12-0114</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr"/>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D176" t="inlineStr">
         <is>
           <t>New York Knicks</t>
@@ -8434,7 +8486,11 @@
           <t>Boston Celtics</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E194" t="n">
         <v>188</v>
       </c>
@@ -8850,7 +8906,11 @@
           <t>Washington Wizards</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E204" t="n">
         <v>197.5</v>
       </c>
@@ -10148,7 +10208,11 @@
           <t>New Jersey Nets</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E235" t="n">
         <v>202</v>
       </c>
@@ -10559,7 +10623,11 @@
           <t>2011-12-0123</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr"/>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D245" t="inlineStr">
         <is>
           <t>Detroit Pistons</t>
@@ -11311,7 +11379,11 @@
           <t>2011-12-0125</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr"/>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D263" t="inlineStr">
         <is>
           <t>New Orleans Pelicans</t>
@@ -12236,7 +12308,11 @@
           <t>Golden State Warriors</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E285" t="n">
         <v>198</v>
       </c>
@@ -13198,7 +13274,11 @@
           <t>Los Angeles Clippers</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E308" t="n">
         <v>196</v>
       </c>
@@ -13824,7 +13904,11 @@
           <t>Dallas Mavericks</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E323" t="n">
         <v>196</v>
       </c>
@@ -14445,7 +14529,11 @@
           <t>2011-12-0203</t>
         </is>
       </c>
-      <c r="C338" t="inlineStr"/>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D338" t="inlineStr">
         <is>
           <t>Memphis Grizzlies</t>
@@ -14992,7 +15080,11 @@
           <t>San Antonio Spurs</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E351" t="n">
         <v>195</v>
       </c>
@@ -15660,7 +15752,11 @@
           <t>Portland Trail Blazers</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr"/>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E367" t="n">
         <v>198</v>
       </c>
@@ -15908,7 +16004,11 @@
           <t>Golden State Warriors</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E373" t="n">
         <v>205.5</v>
       </c>
@@ -16534,7 +16634,11 @@
           <t>Sacramento Kings</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr"/>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E388" t="n">
         <v>202</v>
       </c>
@@ -17034,7 +17138,11 @@
           <t>Utah Jazz</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E400" t="n">
         <v>200.5</v>
       </c>
@@ -18033,7 +18141,11 @@
           <t>2011-12-0214</t>
         </is>
       </c>
-      <c r="C424" t="inlineStr"/>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D424" t="inlineStr">
         <is>
           <t>Utah Jazz</t>
@@ -18580,7 +18692,11 @@
           <t>Houston Rockets</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E437" t="n">
         <v>203.5</v>
       </c>
@@ -19159,7 +19275,11 @@
           <t>2011-12-0217</t>
         </is>
       </c>
-      <c r="C451" t="inlineStr"/>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D451" t="inlineStr">
         <is>
           <t>Golden State Warriors</t>
@@ -19911,7 +20031,11 @@
           <t>2011-12-0219</t>
         </is>
       </c>
-      <c r="C469" t="inlineStr"/>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D469" t="inlineStr">
         <is>
           <t>Denver Nuggets</t>
@@ -20159,7 +20283,11 @@
           <t>2011-12-0220</t>
         </is>
       </c>
-      <c r="C475" t="inlineStr"/>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D475" t="inlineStr">
         <is>
           <t>New Orleans Pelicans</t>
@@ -20701,7 +20829,11 @@
           <t>2011-12-0222</t>
         </is>
       </c>
-      <c r="C488" t="inlineStr"/>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D488" t="inlineStr">
         <is>
           <t>Boston Celtics</t>
@@ -21327,7 +21459,11 @@
           <t>2011-12-0223</t>
         </is>
       </c>
-      <c r="C503" t="inlineStr"/>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D503" t="inlineStr">
         <is>
           <t>Los Angeles Lakers</t>
@@ -21790,7 +21926,11 @@
           <t>Philadelphia 76ers</t>
         </is>
       </c>
-      <c r="D514" t="inlineStr"/>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E514" t="n">
         <v>191</v>
       </c>
@@ -22248,7 +22388,11 @@
           <t>Orlando Magic</t>
         </is>
       </c>
-      <c r="D525" t="inlineStr"/>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E525" t="n">
         <v>192.5</v>
       </c>
@@ -22958,7 +23102,11 @@
           <t>Atlanta Hawks</t>
         </is>
       </c>
-      <c r="D542" t="inlineStr"/>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E542" t="n">
         <v>189.5</v>
       </c>
@@ -23747,7 +23895,11 @@
           <t>2011-12-0305</t>
         </is>
       </c>
-      <c r="C561" t="inlineStr"/>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D561" t="inlineStr">
         <is>
           <t>Dallas Mavericks</t>
@@ -24457,7 +24609,11 @@
           <t>2011-12-0307</t>
         </is>
       </c>
-      <c r="C578" t="inlineStr"/>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D578" t="inlineStr">
         <is>
           <t>Phoenix Suns</t>
@@ -24957,7 +25113,11 @@
           <t>2011-12-0309</t>
         </is>
       </c>
-      <c r="C590" t="inlineStr"/>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D590" t="inlineStr">
         <is>
           <t>Cleveland Cavaliers</t>
@@ -25415,7 +25575,11 @@
           <t>2011-12-0310</t>
         </is>
       </c>
-      <c r="C601" t="inlineStr"/>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D601" t="inlineStr">
         <is>
           <t>Charlotte Bobcats</t>
@@ -26335,7 +26499,11 @@
           <t>2011-12-0313</t>
         </is>
       </c>
-      <c r="C623" t="inlineStr"/>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D623" t="inlineStr">
         <is>
           <t>Houston Rockets</t>
@@ -27092,7 +27260,11 @@
           <t>Denver Nuggets</t>
         </is>
       </c>
-      <c r="D641" t="inlineStr"/>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E641" t="n">
         <v>211</v>
       </c>
@@ -27461,7 +27633,11 @@
           <t>2011-12-0316</t>
         </is>
       </c>
-      <c r="C650" t="inlineStr"/>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D650" t="inlineStr">
         <is>
           <t>San Antonio Spurs</t>
@@ -28255,7 +28431,11 @@
           <t>2011-12-0318</t>
         </is>
       </c>
-      <c r="C669" t="inlineStr"/>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D669" t="inlineStr">
         <is>
           <t>Portland Trail Blazers</t>
@@ -28760,7 +28940,11 @@
           <t>Utah Jazz</t>
         </is>
       </c>
-      <c r="D681" t="inlineStr"/>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E681" t="n">
         <v>204</v>
       </c>
@@ -29129,7 +29313,11 @@
           <t>2011-12-0321</t>
         </is>
       </c>
-      <c r="C690" t="inlineStr"/>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D690" t="inlineStr">
         <is>
           <t>Los Angeles Clippers</t>
@@ -29839,7 +30027,11 @@
           <t>2011-12-0323</t>
         </is>
       </c>
-      <c r="C707" t="inlineStr"/>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D707" t="inlineStr">
         <is>
           <t>Minnesota Timberwolves</t>
@@ -30591,7 +30783,11 @@
           <t>2011-12-0325</t>
         </is>
       </c>
-      <c r="C725" t="inlineStr"/>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D725" t="inlineStr">
         <is>
           <t>Miami Heat</t>
@@ -31306,7 +31502,11 @@
           <t>Portland Trail Blazers</t>
         </is>
       </c>
-      <c r="D742" t="inlineStr"/>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E742" t="n">
         <v>198.5</v>
       </c>
@@ -31932,7 +32132,11 @@
           <t>Los Angeles Lakers</t>
         </is>
       </c>
-      <c r="D757" t="inlineStr"/>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E757" t="n">
         <v>201</v>
       </c>
@@ -32805,7 +33009,11 @@
           <t>2011-12-0401</t>
         </is>
       </c>
-      <c r="C778" t="inlineStr"/>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D778" t="inlineStr">
         <is>
           <t>Chicago Bulls</t>
@@ -33221,7 +33429,11 @@
           <t>2011-12-0402</t>
         </is>
       </c>
-      <c r="C788" t="inlineStr"/>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D788" t="inlineStr">
         <is>
           <t>Memphis Grizzlies</t>
@@ -33894,7 +34106,11 @@
           <t>Miami Heat</t>
         </is>
       </c>
-      <c r="D804" t="inlineStr"/>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E804" t="n">
         <v>197</v>
       </c>
@@ -34394,7 +34610,11 @@
           <t>Indiana Pacers</t>
         </is>
       </c>
-      <c r="D816" t="inlineStr"/>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E816" t="n">
         <v>200</v>
       </c>
@@ -35393,7 +35613,11 @@
           <t>2011-12-0408</t>
         </is>
       </c>
-      <c r="C840" t="inlineStr"/>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D840" t="inlineStr">
         <is>
           <t>Toronto Raptors</t>
@@ -35730,7 +35954,11 @@
           <t>Milwaukee Bucks</t>
         </is>
       </c>
-      <c r="D848" t="inlineStr"/>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E848" t="n">
         <v>210</v>
       </c>
@@ -36477,7 +36705,11 @@
           <t>2011-12-0411</t>
         </is>
       </c>
-      <c r="C866" t="inlineStr"/>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D866" t="inlineStr">
         <is>
           <t>Los Angeles Clippers</t>
@@ -37145,7 +37377,11 @@
           <t>2011-12-0413</t>
         </is>
       </c>
-      <c r="C882" t="inlineStr"/>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D882" t="inlineStr">
         <is>
           <t>Sacramento Kings</t>
@@ -37524,7 +37760,11 @@
           <t>Minnesota Timberwolves</t>
         </is>
       </c>
-      <c r="D891" t="inlineStr"/>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E891" t="n">
         <v>204.5</v>
       </c>
@@ -38444,7 +38684,11 @@
           <t>Los Angeles Clippers</t>
         </is>
       </c>
-      <c r="D913" t="inlineStr"/>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E913" t="n">
         <v>198</v>
       </c>
@@ -39112,7 +39356,11 @@
           <t>Phoenix Suns</t>
         </is>
       </c>
-      <c r="D929" t="inlineStr"/>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E929" t="n">
         <v>207</v>
       </c>
@@ -39696,7 +39944,11 @@
           <t>Sacramento Kings</t>
         </is>
       </c>
-      <c r="D943" t="inlineStr"/>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E943" t="n">
         <v>213</v>
       </c>
@@ -40112,7 +40364,11 @@
           <t>Los Angeles Lakers</t>
         </is>
       </c>
-      <c r="D953" t="inlineStr"/>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E953" t="n">
         <v>200</v>
       </c>
@@ -40733,7 +40989,11 @@
           <t>2011-12-0424</t>
         </is>
       </c>
-      <c r="C968" t="inlineStr"/>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D968" t="inlineStr">
         <is>
           <t>Sacramento Kings</t>
@@ -41023,7 +41283,11 @@
           <t>2011-12-0425</t>
         </is>
       </c>
-      <c r="C975" t="inlineStr"/>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D975" t="inlineStr">
         <is>
           <t>Denver Nuggets</t>
@@ -41859,7 +42123,11 @@
           <t>2011-12-0428</t>
         </is>
       </c>
-      <c r="C995" t="inlineStr"/>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D995" t="inlineStr">
         <is>
           <t>Dallas Mavericks</t>
@@ -42149,7 +42417,11 @@
           <t>2011-12-0430</t>
         </is>
       </c>
-      <c r="C1002" t="inlineStr"/>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D1002" t="inlineStr">
         <is>
           <t>Dallas Mavericks</t>
@@ -42486,7 +42758,11 @@
           <t>Dallas Mavericks</t>
         </is>
       </c>
-      <c r="D1010" t="inlineStr"/>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E1010" t="n">
         <v>196</v>
       </c>
@@ -42734,7 +43010,11 @@
           <t>Dallas Mavericks</t>
         </is>
       </c>
-      <c r="D1016" t="inlineStr"/>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E1016" t="n">
         <v>192.5</v>
       </c>
@@ -43649,7 +43929,11 @@
           <t>2011-12-0514</t>
         </is>
       </c>
-      <c r="C1038" t="inlineStr"/>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D1038" t="inlineStr">
         <is>
           <t>Los Angeles Lakers</t>
@@ -43855,7 +44139,11 @@
           <t>2011-12-0516</t>
         </is>
       </c>
-      <c r="C1043" t="inlineStr"/>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D1043" t="inlineStr">
         <is>
           <t>Los Angeles Lakers</t>
@@ -44024,7 +44312,11 @@
           <t>Los Angeles Lakers</t>
         </is>
       </c>
-      <c r="D1047" t="inlineStr"/>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E1047" t="n">
         <v>194</v>
       </c>
@@ -44104,7 +44396,11 @@
           <t>Los Angeles Lakers</t>
         </is>
       </c>
-      <c r="D1049" t="inlineStr"/>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E1049" t="n">
         <v>191</v>
       </c>
@@ -44263,7 +44559,11 @@
           <t>2011-12-0521</t>
         </is>
       </c>
-      <c r="C1053" t="inlineStr"/>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D1053" t="inlineStr">
         <is>
           <t>Los Angeles Lakers</t>
@@ -44474,7 +44774,11 @@
           <t>San Antonio Spurs</t>
         </is>
       </c>
-      <c r="D1058" t="inlineStr"/>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E1058" t="n">
         <v>201</v>
       </c>
@@ -44554,7 +44858,11 @@
           <t>San Antonio Spurs</t>
         </is>
       </c>
-      <c r="D1060" t="inlineStr"/>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E1060" t="n">
         <v>202</v>
       </c>
@@ -44629,7 +44937,11 @@
           <t>2011-12-0531</t>
         </is>
       </c>
-      <c r="C1062" t="inlineStr"/>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D1062" t="inlineStr">
         <is>
           <t>San Antonio Spurs</t>
@@ -44709,7 +45021,11 @@
           <t>2011-12-0602</t>
         </is>
       </c>
-      <c r="C1064" t="inlineStr"/>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D1064" t="inlineStr">
         <is>
           <t>San Antonio Spurs</t>
@@ -44794,7 +45110,11 @@
           <t>San Antonio Spurs</t>
         </is>
       </c>
-      <c r="D1066" t="inlineStr"/>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E1066" t="n">
         <v>203.5</v>
       </c>
@@ -44869,7 +45189,11 @@
           <t>2011-12-0606</t>
         </is>
       </c>
-      <c r="C1068" t="inlineStr"/>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D1068" t="inlineStr">
         <is>
           <t>San Antonio Spurs</t>
@@ -44991,7 +45315,11 @@
           <t>2011-12-0612</t>
         </is>
       </c>
-      <c r="C1071" t="inlineStr"/>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D1071" t="inlineStr">
         <is>
           <t>Miami Heat</t>
@@ -45029,7 +45357,11 @@
           <t>2011-12-0614</t>
         </is>
       </c>
-      <c r="C1072" t="inlineStr"/>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="D1072" t="inlineStr">
         <is>
           <t>Miami Heat</t>
@@ -45072,7 +45404,11 @@
           <t>Miami Heat</t>
         </is>
       </c>
-      <c r="D1073" t="inlineStr"/>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E1073" t="n">
         <v>195</v>
       </c>
@@ -45110,7 +45446,11 @@
           <t>Miami Heat</t>
         </is>
       </c>
-      <c r="D1074" t="inlineStr"/>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E1074" t="n">
         <v>192</v>
       </c>
@@ -45148,7 +45488,11 @@
           <t>Miami Heat</t>
         </is>
       </c>
-      <c r="D1075" t="inlineStr"/>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
       <c r="E1075" t="n">
         <v>193</v>
       </c>
@@ -45173,6 +45517,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>